--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY107"/>
+  <dimension ref="A1:AY123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12625,6 +12625,1794 @@
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>114993651</v>
+      </c>
+      <c r="B108" t="n">
+        <v>56450</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>801124</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7496216</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Spår och spillning.</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>114993699</v>
+      </c>
+      <c r="B109" t="n">
+        <v>78555</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>864</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>800899</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7496209</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>114993786</v>
+      </c>
+      <c r="B110" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>801205</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7496262</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Skalad gran från födosökande tretåig hackspett.</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>114993762</v>
+      </c>
+      <c r="B111" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>801353</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7496440</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Äldre ringhackning på björk.</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>114993646</v>
+      </c>
+      <c r="B112" t="n">
+        <v>90278</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>801124</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7496216</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>114993746</v>
+      </c>
+      <c r="B113" t="n">
+        <v>90278</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>800968</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7496401</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>114993650</v>
+      </c>
+      <c r="B114" t="n">
+        <v>78473</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>801124</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7496216</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Rikligt draperade granar</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114993669</v>
+      </c>
+      <c r="B115" t="n">
+        <v>78555</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>864</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>801036</v>
+      </c>
+      <c r="R115" t="n">
+        <v>7496140</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>114993700</v>
+      </c>
+      <c r="B116" t="n">
+        <v>78473</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>800899</v>
+      </c>
+      <c r="R116" t="n">
+        <v>7496209</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Rikligt draperade granar</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>114993757</v>
+      </c>
+      <c r="B117" t="n">
+        <v>56442</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>801353</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7496440</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>114993674</v>
+      </c>
+      <c r="B118" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>801036</v>
+      </c>
+      <c r="R118" t="n">
+        <v>7496140</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ringhackning på tall</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>114993749</v>
+      </c>
+      <c r="B119" t="n">
+        <v>56450</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>800985</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7496433</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>114993706</v>
+      </c>
+      <c r="B120" t="n">
+        <v>90278</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>800906</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7496322</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>114993742</v>
+      </c>
+      <c r="B121" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>800958</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7496350</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Färsk ringhackning på tall.</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>114993701</v>
+      </c>
+      <c r="B122" t="n">
+        <v>57343</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>800912</v>
+      </c>
+      <c r="R122" t="n">
+        <v>7496271</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>114993703</v>
+      </c>
+      <c r="B123" t="n">
+        <v>78473</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>800912</v>
+      </c>
+      <c r="R123" t="n">
+        <v>7496271</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Rikligt draperade granar</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -23819,10 +23819,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>117493440</v>
+        <v>117493849</v>
       </c>
       <c r="B210" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23835,26 +23835,31 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
@@ -23862,10 +23867,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>801417</v>
+        <v>801529</v>
       </c>
       <c r="R210" t="n">
-        <v>7497205</v>
+        <v>7496739</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23900,13 +23905,17 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>Mindre gran skalad på bark i små bitar som låg runt på marken.</t>
+        </is>
+      </c>
       <c r="AD210" t="b">
         <v>0</v>
       </c>
       <c r="AE210" t="b">
         <v>0</v>
       </c>
-      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
@@ -23925,7 +23934,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>117493465</v>
+        <v>117493440</v>
       </c>
       <c r="B211" t="n">
         <v>90517</v>
@@ -23968,10 +23977,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>801438</v>
+        <v>801417</v>
       </c>
       <c r="R211" t="n">
-        <v>7497203</v>
+        <v>7497205</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -24031,10 +24040,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>117493849</v>
+        <v>117493465</v>
       </c>
       <c r="B212" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -24047,31 +24056,26 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
@@ -24079,10 +24083,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>801529</v>
+        <v>801438</v>
       </c>
       <c r="R212" t="n">
-        <v>7496739</v>
+        <v>7497203</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24117,17 +24121,13 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>Mindre gran skalad på bark i små bitar som låg runt på marken.</t>
-        </is>
-      </c>
       <c r="AD212" t="b">
         <v>0</v>
       </c>
       <c r="AE212" t="b">
         <v>0</v>
       </c>
+      <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
       </c>
@@ -27265,10 +27265,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>117823815</v>
+        <v>117823874</v>
       </c>
       <c r="B242" t="n">
-        <v>56499</v>
+        <v>90499</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -27277,43 +27277,30 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
@@ -27321,10 +27308,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>801037</v>
+        <v>800985</v>
       </c>
       <c r="R242" t="n">
-        <v>7496692</v>
+        <v>7496417</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27365,6 +27352,7 @@
       <c r="AE242" t="b">
         <v>0</v>
       </c>
+      <c r="AF242" t="inlineStr"/>
       <c r="AG242" t="b">
         <v>0</v>
       </c>
@@ -27383,10 +27371,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>117823930</v>
+        <v>117824245</v>
       </c>
       <c r="B243" t="n">
-        <v>57436</v>
+        <v>90517</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -27399,35 +27387,26 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>103022</v>
+        <v>5432</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
-        </is>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
@@ -27438,7 +27417,7 @@
         <v>801237</v>
       </c>
       <c r="R243" t="n">
-        <v>7496086</v>
+        <v>7496799</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27479,6 +27458,7 @@
       <c r="AE243" t="b">
         <v>0</v>
       </c>
+      <c r="AF243" t="inlineStr"/>
       <c r="AG243" t="b">
         <v>0</v>
       </c>
@@ -27497,10 +27477,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>117823874</v>
+        <v>117824142</v>
       </c>
       <c r="B244" t="n">
-        <v>90499</v>
+        <v>90517</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -27513,21 +27493,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -27540,10 +27520,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>800985</v>
+        <v>801377</v>
       </c>
       <c r="R244" t="n">
-        <v>7496417</v>
+        <v>7496244</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -27603,7 +27583,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>117824245</v>
+        <v>117823842</v>
       </c>
       <c r="B245" t="n">
         <v>90517</v>
@@ -27646,10 +27626,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>801237</v>
+        <v>801035</v>
       </c>
       <c r="R245" t="n">
-        <v>7496799</v>
+        <v>7496536</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -27709,10 +27689,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>117824142</v>
+        <v>117823815</v>
       </c>
       <c r="B246" t="n">
-        <v>90517</v>
+        <v>56499</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -27721,30 +27701,43 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
@@ -27752,10 +27745,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>801377</v>
+        <v>801037</v>
       </c>
       <c r="R246" t="n">
-        <v>7496244</v>
+        <v>7496692</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -27796,7 +27789,6 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
-      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
@@ -27815,10 +27807,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>117823842</v>
+        <v>117823930</v>
       </c>
       <c r="B247" t="n">
-        <v>90517</v>
+        <v>57436</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -27831,26 +27823,35 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>5432</v>
+        <v>103022</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr"/>
-      <c r="J247" t="inlineStr"/>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
@@ -27858,10 +27859,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>801035</v>
+        <v>801237</v>
       </c>
       <c r="R247" t="n">
-        <v>7496536</v>
+        <v>7496086</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -27902,7 +27903,6 @@
       <c r="AE247" t="b">
         <v>0</v>
       </c>
-      <c r="AF247" t="inlineStr"/>
       <c r="AG247" t="b">
         <v>0</v>
       </c>
@@ -28463,10 +28463,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>117823850</v>
+        <v>117823716</v>
       </c>
       <c r="B253" t="n">
-        <v>78562</v>
+        <v>78480</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -28479,21 +28479,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28506,10 +28506,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>801035</v>
+        <v>801141</v>
       </c>
       <c r="R253" t="n">
-        <v>7496536</v>
+        <v>7496945</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28569,10 +28569,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>117823893</v>
+        <v>117823850</v>
       </c>
       <c r="B254" t="n">
-        <v>90782</v>
+        <v>78562</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -28585,21 +28585,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -28612,10 +28612,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>800994</v>
+        <v>801035</v>
       </c>
       <c r="R254" t="n">
-        <v>7496425</v>
+        <v>7496536</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28675,10 +28675,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>117823716</v>
+        <v>117823893</v>
       </c>
       <c r="B255" t="n">
-        <v>78480</v>
+        <v>90782</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -28691,21 +28691,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -28718,10 +28718,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>801141</v>
+        <v>800994</v>
       </c>
       <c r="R255" t="n">
-        <v>7496945</v>
+        <v>7496425</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -20265,7 +20265,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>117493964</v>
+        <v>117493950</v>
       </c>
       <c r="B177" t="n">
         <v>90782</v>
@@ -20308,10 +20308,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>801235</v>
+        <v>801270</v>
       </c>
       <c r="R177" t="n">
-        <v>7496982</v>
+        <v>7496960</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20371,10 +20371,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>117493545</v>
+        <v>117493440</v>
       </c>
       <c r="B178" t="n">
-        <v>56491</v>
+        <v>90517</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20387,35 +20387,26 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
@@ -20423,10 +20414,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>801515</v>
+        <v>801417</v>
       </c>
       <c r="R178" t="n">
-        <v>7497168</v>
+        <v>7497205</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20467,6 +20458,7 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -20485,10 +20477,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>117493718</v>
+        <v>117493790</v>
       </c>
       <c r="B179" t="n">
-        <v>90782</v>
+        <v>57303</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20501,26 +20493,31 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
@@ -20528,10 +20525,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>801713</v>
+        <v>801649</v>
       </c>
       <c r="R179" t="n">
-        <v>7497045</v>
+        <v>7496917</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20566,13 +20563,17 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Skalad björk</t>
+        </is>
+      </c>
       <c r="AD179" t="b">
         <v>0</v>
       </c>
       <c r="AE179" t="b">
         <v>0</v>
       </c>
-      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
@@ -20591,10 +20592,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>117493561</v>
+        <v>117493421</v>
       </c>
       <c r="B180" t="n">
-        <v>90517</v>
+        <v>57656</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20603,41 +20604,54 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>801519</v>
+        <v>801393</v>
       </c>
       <c r="R180" t="n">
-        <v>7497181</v>
+        <v>7497245</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20678,7 +20692,6 @@
       <c r="AE180" t="b">
         <v>0</v>
       </c>
-      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
@@ -20697,10 +20710,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>117493421</v>
+        <v>117493814</v>
       </c>
       <c r="B181" t="n">
-        <v>57656</v>
+        <v>90688</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20709,54 +20722,41 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>103015</v>
+        <v>48</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>801393</v>
+        <v>801529</v>
       </c>
       <c r="R181" t="n">
-        <v>7497245</v>
+        <v>7496739</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20797,6 +20797,7 @@
       <c r="AE181" t="b">
         <v>0</v>
       </c>
+      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
       </c>
@@ -20815,10 +20816,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>117493766</v>
+        <v>117493718</v>
       </c>
       <c r="B182" t="n">
-        <v>78480</v>
+        <v>90782</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20831,21 +20832,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -20858,10 +20859,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>801686</v>
+        <v>801713</v>
       </c>
       <c r="R182" t="n">
-        <v>7496943</v>
+        <v>7497045</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20921,10 +20922,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>117493814</v>
+        <v>117493495</v>
       </c>
       <c r="B183" t="n">
-        <v>90688</v>
+        <v>90782</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20933,25 +20934,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20964,10 +20965,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>801529</v>
+        <v>801505</v>
       </c>
       <c r="R183" t="n">
-        <v>7496739</v>
+        <v>7497188</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21027,10 +21028,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>117493966</v>
+        <v>117494135</v>
       </c>
       <c r="B184" t="n">
-        <v>90499</v>
+        <v>57303</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21043,26 +21044,31 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
@@ -21070,10 +21076,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>801235</v>
+        <v>801271</v>
       </c>
       <c r="R184" t="n">
-        <v>7496982</v>
+        <v>7497120</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21108,13 +21114,17 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>Stort hål hackad i torrgran, möjligtvis ett boträd</t>
+        </is>
+      </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
       <c r="AE184" t="b">
         <v>0</v>
       </c>
-      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
@@ -21239,10 +21249,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>117494153</v>
+        <v>117493545</v>
       </c>
       <c r="B186" t="n">
-        <v>90517</v>
+        <v>56491</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21255,26 +21265,35 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
@@ -21282,10 +21301,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>801294</v>
+        <v>801515</v>
       </c>
       <c r="R186" t="n">
-        <v>7497230</v>
+        <v>7497168</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21326,7 +21345,6 @@
       <c r="AE186" t="b">
         <v>0</v>
       </c>
-      <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
       </c>
@@ -21345,10 +21363,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>117493800</v>
+        <v>117493966</v>
       </c>
       <c r="B187" t="n">
-        <v>90517</v>
+        <v>90499</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21361,21 +21379,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -21388,10 +21406,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>801538</v>
+        <v>801235</v>
       </c>
       <c r="R187" t="n">
-        <v>7496766</v>
+        <v>7496982</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21451,10 +21469,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>117493950</v>
+        <v>117493465</v>
       </c>
       <c r="B188" t="n">
-        <v>90782</v>
+        <v>90517</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21467,21 +21485,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -21494,10 +21512,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>801270</v>
+        <v>801438</v>
       </c>
       <c r="R188" t="n">
-        <v>7496960</v>
+        <v>7497203</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21672,10 +21690,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>117493927</v>
+        <v>117493541</v>
       </c>
       <c r="B190" t="n">
-        <v>90782</v>
+        <v>90499</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21688,21 +21706,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21715,10 +21733,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>801276</v>
+        <v>801515</v>
       </c>
       <c r="R190" t="n">
-        <v>7496938</v>
+        <v>7497168</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21778,10 +21796,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>117493500</v>
+        <v>117494050</v>
       </c>
       <c r="B191" t="n">
-        <v>90499</v>
+        <v>78480</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -21794,21 +21812,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -21821,10 +21839,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>801505</v>
+        <v>801235</v>
       </c>
       <c r="R191" t="n">
-        <v>7497188</v>
+        <v>7497122</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21884,10 +21902,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>117493930</v>
+        <v>117493818</v>
       </c>
       <c r="B192" t="n">
-        <v>90464</v>
+        <v>90782</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -21896,25 +21914,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21927,10 +21945,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>801276</v>
+        <v>801529</v>
       </c>
       <c r="R192" t="n">
-        <v>7496938</v>
+        <v>7496739</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21990,10 +22008,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>117493495</v>
+        <v>117493766</v>
       </c>
       <c r="B193" t="n">
-        <v>90782</v>
+        <v>78480</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22006,21 +22024,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -22033,10 +22051,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>801505</v>
+        <v>801686</v>
       </c>
       <c r="R193" t="n">
-        <v>7497188</v>
+        <v>7496943</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22096,10 +22114,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>117493541</v>
+        <v>117493800</v>
       </c>
       <c r="B194" t="n">
-        <v>90499</v>
+        <v>90517</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22112,21 +22130,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -22139,10 +22157,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>801515</v>
+        <v>801538</v>
       </c>
       <c r="R194" t="n">
-        <v>7497168</v>
+        <v>7496766</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22202,10 +22220,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>117493978</v>
+        <v>117493585</v>
       </c>
       <c r="B195" t="n">
-        <v>90517</v>
+        <v>78480</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22218,21 +22236,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -22245,10 +22263,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>801204</v>
+        <v>801555</v>
       </c>
       <c r="R195" t="n">
-        <v>7497033</v>
+        <v>7497160</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22308,10 +22326,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>117493571</v>
+        <v>117493892</v>
       </c>
       <c r="B196" t="n">
-        <v>78480</v>
+        <v>90517</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22324,21 +22342,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -22351,10 +22369,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>801551</v>
+        <v>801386</v>
       </c>
       <c r="R196" t="n">
-        <v>7497149</v>
+        <v>7496874</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22414,10 +22432,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>117494135</v>
+        <v>117493964</v>
       </c>
       <c r="B197" t="n">
-        <v>57303</v>
+        <v>90782</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22430,31 +22448,26 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
@@ -22462,10 +22475,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>801271</v>
+        <v>801235</v>
       </c>
       <c r="R197" t="n">
-        <v>7497120</v>
+        <v>7496982</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22500,17 +22513,13 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>Stort hål hackad i torrgran, möjligtvis ett boträd</t>
-        </is>
-      </c>
       <c r="AD197" t="b">
         <v>0</v>
       </c>
       <c r="AE197" t="b">
         <v>0</v>
       </c>
+      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
@@ -22529,10 +22538,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>117494041</v>
+        <v>117493906</v>
       </c>
       <c r="B198" t="n">
-        <v>57287</v>
+        <v>78480</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22545,31 +22554,26 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
@@ -22577,10 +22581,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>801235</v>
+        <v>801379</v>
       </c>
       <c r="R198" t="n">
-        <v>7497122</v>
+        <v>7496877</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22615,17 +22619,13 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>Gran skalad på små barkflagor och dessa låg runt på marken.</t>
-        </is>
-      </c>
       <c r="AD198" t="b">
         <v>0</v>
       </c>
       <c r="AE198" t="b">
         <v>0</v>
       </c>
+      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
       </c>
@@ -22644,10 +22644,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>117493725</v>
+        <v>117494153</v>
       </c>
       <c r="B199" t="n">
-        <v>90688</v>
+        <v>90517</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22656,25 +22656,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>48</v>
+        <v>5432</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -22687,10 +22687,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>801713</v>
+        <v>801294</v>
       </c>
       <c r="R199" t="n">
-        <v>7497045</v>
+        <v>7497230</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22750,10 +22750,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>117493818</v>
+        <v>117493978</v>
       </c>
       <c r="B200" t="n">
-        <v>90782</v>
+        <v>90517</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22766,21 +22766,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22793,10 +22793,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>801529</v>
+        <v>801204</v>
       </c>
       <c r="R200" t="n">
-        <v>7496739</v>
+        <v>7497033</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22856,10 +22856,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>117493924</v>
+        <v>117493571</v>
       </c>
       <c r="B201" t="n">
-        <v>90688</v>
+        <v>78480</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22868,25 +22868,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>48</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -22899,10 +22899,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>801276</v>
+        <v>801551</v>
       </c>
       <c r="R201" t="n">
-        <v>7496938</v>
+        <v>7497149</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22962,10 +22962,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>117493446</v>
+        <v>117493927</v>
       </c>
       <c r="B202" t="n">
-        <v>78480</v>
+        <v>90782</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22978,21 +22978,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -23005,10 +23005,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>801417</v>
+        <v>801276</v>
       </c>
       <c r="R202" t="n">
-        <v>7497205</v>
+        <v>7496938</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -23068,10 +23068,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>117493892</v>
+        <v>117494041</v>
       </c>
       <c r="B203" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23084,26 +23084,31 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
@@ -23111,10 +23116,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>801386</v>
+        <v>801235</v>
       </c>
       <c r="R203" t="n">
-        <v>7496874</v>
+        <v>7497122</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23149,13 +23154,17 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>Gran skalad på små barkflagor och dessa låg runt på marken.</t>
+        </is>
+      </c>
       <c r="AD203" t="b">
         <v>0</v>
       </c>
       <c r="AE203" t="b">
         <v>0</v>
       </c>
-      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
@@ -23174,10 +23183,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>117494050</v>
+        <v>117493849</v>
       </c>
       <c r="B204" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23190,26 +23199,31 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
@@ -23217,10 +23231,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>801235</v>
+        <v>801529</v>
       </c>
       <c r="R204" t="n">
-        <v>7497122</v>
+        <v>7496739</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23255,13 +23269,17 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>Mindre gran skalad på bark i små bitar som låg runt på marken.</t>
+        </is>
+      </c>
       <c r="AD204" t="b">
         <v>0</v>
       </c>
       <c r="AE204" t="b">
         <v>0</v>
       </c>
-      <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="b">
         <v>0</v>
       </c>
@@ -23280,10 +23298,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>117493906</v>
+        <v>117493500</v>
       </c>
       <c r="B205" t="n">
-        <v>78480</v>
+        <v>90499</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23296,21 +23314,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -23323,10 +23341,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>801379</v>
+        <v>801505</v>
       </c>
       <c r="R205" t="n">
-        <v>7496877</v>
+        <v>7497188</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23386,10 +23404,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>117493790</v>
+        <v>117493446</v>
       </c>
       <c r="B206" t="n">
-        <v>57303</v>
+        <v>78480</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23402,31 +23420,26 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
@@ -23434,10 +23447,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>801649</v>
+        <v>801417</v>
       </c>
       <c r="R206" t="n">
-        <v>7496917</v>
+        <v>7497205</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23472,17 +23485,13 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>Skalad björk</t>
-        </is>
-      </c>
       <c r="AD206" t="b">
         <v>0</v>
       </c>
       <c r="AE206" t="b">
         <v>0</v>
       </c>
+      <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="b">
         <v>0</v>
       </c>
@@ -23501,10 +23510,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>117494044</v>
+        <v>117493930</v>
       </c>
       <c r="B207" t="n">
-        <v>90517</v>
+        <v>90464</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23513,25 +23522,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -23544,10 +23553,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>801235</v>
+        <v>801276</v>
       </c>
       <c r="R207" t="n">
-        <v>7497122</v>
+        <v>7496938</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23607,10 +23616,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>117493531</v>
+        <v>117494044</v>
       </c>
       <c r="B208" t="n">
-        <v>90782</v>
+        <v>90517</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -23623,21 +23632,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23650,10 +23659,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>801515</v>
+        <v>801235</v>
       </c>
       <c r="R208" t="n">
-        <v>7497168</v>
+        <v>7497122</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23713,10 +23722,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>117493585</v>
+        <v>117493725</v>
       </c>
       <c r="B209" t="n">
-        <v>78480</v>
+        <v>90688</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -23725,25 +23734,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6425</v>
+        <v>48</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -23756,10 +23765,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>801555</v>
+        <v>801713</v>
       </c>
       <c r="R209" t="n">
-        <v>7497160</v>
+        <v>7497045</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23819,10 +23828,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>117493849</v>
+        <v>117493561</v>
       </c>
       <c r="B210" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23835,31 +23844,26 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
@@ -23867,10 +23871,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>801529</v>
+        <v>801519</v>
       </c>
       <c r="R210" t="n">
-        <v>7496739</v>
+        <v>7497181</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23905,17 +23909,13 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>Mindre gran skalad på bark i små bitar som låg runt på marken.</t>
-        </is>
-      </c>
       <c r="AD210" t="b">
         <v>0</v>
       </c>
       <c r="AE210" t="b">
         <v>0</v>
       </c>
+      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
@@ -23934,10 +23934,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>117493440</v>
+        <v>117493583</v>
       </c>
       <c r="B211" t="n">
-        <v>90517</v>
+        <v>90513</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -23950,21 +23950,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23977,10 +23977,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>801417</v>
+        <v>801555</v>
       </c>
       <c r="R211" t="n">
-        <v>7497205</v>
+        <v>7497160</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -24040,10 +24040,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>117493465</v>
+        <v>117493924</v>
       </c>
       <c r="B212" t="n">
-        <v>90517</v>
+        <v>90688</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -24052,25 +24052,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>5432</v>
+        <v>48</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -24083,10 +24083,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>801438</v>
+        <v>801276</v>
       </c>
       <c r="R212" t="n">
-        <v>7497203</v>
+        <v>7496938</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24146,10 +24146,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>117493583</v>
+        <v>117493531</v>
       </c>
       <c r="B213" t="n">
-        <v>90513</v>
+        <v>90782</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24162,21 +24162,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -24189,10 +24189,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>801555</v>
+        <v>801515</v>
       </c>
       <c r="R213" t="n">
-        <v>7497160</v>
+        <v>7497168</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -24252,10 +24252,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>117823847</v>
+        <v>117823915</v>
       </c>
       <c r="B214" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24268,26 +24268,31 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
@@ -24295,10 +24300,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>801035</v>
+        <v>800952</v>
       </c>
       <c r="R214" t="n">
-        <v>7496536</v>
+        <v>7496369</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24333,13 +24338,17 @@
           <t>2024-06-16</t>
         </is>
       </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD214" t="b">
         <v>0</v>
       </c>
       <c r="AE214" t="b">
         <v>0</v>
       </c>
-      <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
       </c>
@@ -24358,7 +24367,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>117823827</v>
+        <v>117824142</v>
       </c>
       <c r="B215" t="n">
         <v>90517</v>
@@ -24401,10 +24410,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>801032</v>
+        <v>801377</v>
       </c>
       <c r="R215" t="n">
-        <v>7496586</v>
+        <v>7496244</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24464,10 +24473,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>117823771</v>
+        <v>117823805</v>
       </c>
       <c r="B216" t="n">
-        <v>90517</v>
+        <v>78480</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24480,21 +24489,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -24507,10 +24516,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>801053</v>
+        <v>801037</v>
       </c>
       <c r="R216" t="n">
-        <v>7496754</v>
+        <v>7496692</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24570,10 +24579,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>117823915</v>
+        <v>117824122</v>
       </c>
       <c r="B217" t="n">
-        <v>57287</v>
+        <v>90941</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24582,35 +24591,30 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
@@ -24618,10 +24622,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>800952</v>
+        <v>801408</v>
       </c>
       <c r="R217" t="n">
-        <v>7496369</v>
+        <v>7496150</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24656,17 +24660,13 @@
           <t>2024-06-16</t>
         </is>
       </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD217" t="b">
         <v>0</v>
       </c>
       <c r="AE217" t="b">
         <v>0</v>
       </c>
+      <c r="AF217" t="inlineStr"/>
       <c r="AG217" t="b">
         <v>0</v>
       </c>
@@ -24685,10 +24685,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>117823891</v>
+        <v>117824279</v>
       </c>
       <c r="B218" t="n">
-        <v>90499</v>
+        <v>90517</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24701,21 +24701,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24728,10 +24728,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>800994</v>
+        <v>801279</v>
       </c>
       <c r="R218" t="n">
-        <v>7496425</v>
+        <v>7496824</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24791,7 +24791,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>117824290</v>
+        <v>117824182</v>
       </c>
       <c r="B219" t="n">
         <v>90517</v>
@@ -24834,10 +24834,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>801321</v>
+        <v>801234</v>
       </c>
       <c r="R219" t="n">
-        <v>7497019</v>
+        <v>7496578</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24897,10 +24897,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>117823789</v>
+        <v>117824177</v>
       </c>
       <c r="B220" t="n">
-        <v>90517</v>
+        <v>90852</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -24909,25 +24909,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -24940,10 +24940,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>801037</v>
+        <v>801234</v>
       </c>
       <c r="R220" t="n">
-        <v>7496692</v>
+        <v>7496578</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25003,10 +25003,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>117823972</v>
+        <v>117824004</v>
       </c>
       <c r="B221" t="n">
-        <v>91064</v>
+        <v>78480</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -25015,25 +25015,25 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -25046,10 +25046,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>801391</v>
+        <v>801445</v>
       </c>
       <c r="R221" t="n">
-        <v>7496026</v>
+        <v>7496018</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25082,6 +25082,11 @@
       <c r="AA221" t="inlineStr">
         <is>
           <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>Rikligt draperade granar</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -25109,10 +25114,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>117824160</v>
+        <v>117823847</v>
       </c>
       <c r="B222" t="n">
-        <v>90852</v>
+        <v>78480</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -25121,25 +25126,25 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -25152,10 +25157,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>801351</v>
+        <v>801035</v>
       </c>
       <c r="R222" t="n">
-        <v>7496276</v>
+        <v>7496536</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25215,10 +25220,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>117823794</v>
+        <v>117823881</v>
       </c>
       <c r="B223" t="n">
-        <v>90688</v>
+        <v>78480</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -25227,25 +25232,25 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>48</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -25258,10 +25263,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>801037</v>
+        <v>800985</v>
       </c>
       <c r="R223" t="n">
-        <v>7496692</v>
+        <v>7496417</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25427,10 +25432,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>117823981</v>
+        <v>117823862</v>
       </c>
       <c r="B225" t="n">
-        <v>78480</v>
+        <v>90517</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -25443,21 +25448,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -25470,10 +25475,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>801391</v>
+        <v>801027</v>
       </c>
       <c r="R225" t="n">
-        <v>7496026</v>
+        <v>7496436</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25506,11 +25511,6 @@
       <c r="AA225" t="inlineStr">
         <is>
           <t>2024-06-16</t>
-        </is>
-      </c>
-      <c r="AC225" t="inlineStr">
-        <is>
-          <t>Rikligt draperade granar</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25538,10 +25538,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>117824164</v>
+        <v>117823716</v>
       </c>
       <c r="B226" t="n">
-        <v>90517</v>
+        <v>78480</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -25554,21 +25554,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -25581,10 +25581,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>801351</v>
+        <v>801141</v>
       </c>
       <c r="R226" t="n">
-        <v>7496276</v>
+        <v>7496945</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25644,10 +25644,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>117824122</v>
+        <v>117823874</v>
       </c>
       <c r="B227" t="n">
-        <v>90941</v>
+        <v>90499</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -25656,25 +25656,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -25687,10 +25687,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>801408</v>
+        <v>800985</v>
       </c>
       <c r="R227" t="n">
-        <v>7496150</v>
+        <v>7496417</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25856,10 +25856,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>117824279</v>
+        <v>117823794</v>
       </c>
       <c r="B229" t="n">
-        <v>90517</v>
+        <v>90688</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -25868,25 +25868,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>5432</v>
+        <v>48</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -25899,10 +25899,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>801279</v>
+        <v>801037</v>
       </c>
       <c r="R229" t="n">
-        <v>7496824</v>
+        <v>7496692</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25962,10 +25962,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>117824147</v>
+        <v>117824025</v>
       </c>
       <c r="B230" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -25978,31 +25978,26 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
@@ -26010,10 +26005,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>801377</v>
+        <v>801459</v>
       </c>
       <c r="R230" t="n">
-        <v>7496244</v>
+        <v>7496022</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -26048,17 +26043,13 @@
           <t>2024-06-16</t>
         </is>
       </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>Ringhackning på björk</t>
-        </is>
-      </c>
       <c r="AD230" t="b">
         <v>0</v>
       </c>
       <c r="AE230" t="b">
         <v>0</v>
       </c>
+      <c r="AF230" t="inlineStr"/>
       <c r="AG230" t="b">
         <v>0</v>
       </c>
@@ -26077,10 +26068,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>117824252</v>
+        <v>117823981</v>
       </c>
       <c r="B231" t="n">
-        <v>57656</v>
+        <v>78480</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -26089,39 +26080,30 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
@@ -26129,10 +26111,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>801237</v>
+        <v>801391</v>
       </c>
       <c r="R231" t="n">
-        <v>7496799</v>
+        <v>7496026</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26167,12 +26149,18 @@
           <t>2024-06-16</t>
         </is>
       </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>Rikligt draperade granar</t>
+        </is>
+      </c>
       <c r="AD231" t="b">
         <v>0</v>
       </c>
       <c r="AE231" t="b">
         <v>0</v>
       </c>
+      <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="b">
         <v>0</v>
       </c>
@@ -26191,7 +26179,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>117823690</v>
+        <v>117824147</v>
       </c>
       <c r="B232" t="n">
         <v>57287</v>
@@ -26239,10 +26227,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>801141</v>
+        <v>801377</v>
       </c>
       <c r="R232" t="n">
-        <v>7496945</v>
+        <v>7496244</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26279,7 +26267,7 @@
       </c>
       <c r="AC232" t="inlineStr">
         <is>
-          <t>Skalad gran</t>
+          <t>Ringhackning på björk</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26306,10 +26294,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>117823881</v>
+        <v>117824252</v>
       </c>
       <c r="B233" t="n">
-        <v>78480</v>
+        <v>57656</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -26318,30 +26306,39 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr"/>
-      <c r="J233" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
@@ -26349,10 +26346,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>800985</v>
+        <v>801237</v>
       </c>
       <c r="R233" t="n">
-        <v>7496417</v>
+        <v>7496799</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26393,7 +26390,6 @@
       <c r="AE233" t="b">
         <v>0</v>
       </c>
-      <c r="AF233" t="inlineStr"/>
       <c r="AG233" t="b">
         <v>0</v>
       </c>
@@ -26412,7 +26408,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>117823862</v>
+        <v>117823842</v>
       </c>
       <c r="B234" t="n">
         <v>90517</v>
@@ -26455,10 +26451,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>801027</v>
+        <v>801035</v>
       </c>
       <c r="R234" t="n">
-        <v>7496436</v>
+        <v>7496536</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26518,10 +26514,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>117823798</v>
+        <v>117824022</v>
       </c>
       <c r="B235" t="n">
-        <v>90782</v>
+        <v>91195</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -26530,25 +26526,25 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>658</v>
+        <v>67</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -26561,10 +26557,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>801037</v>
+        <v>801459</v>
       </c>
       <c r="R235" t="n">
-        <v>7496692</v>
+        <v>7496022</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -26624,10 +26620,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>117824022</v>
+        <v>117824290</v>
       </c>
       <c r="B236" t="n">
-        <v>91195</v>
+        <v>90517</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -26636,25 +26632,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>67</v>
+        <v>5432</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -26667,10 +26663,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>801459</v>
+        <v>801321</v>
       </c>
       <c r="R236" t="n">
-        <v>7496022</v>
+        <v>7497019</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26730,10 +26726,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>117823805</v>
+        <v>117823999</v>
       </c>
       <c r="B237" t="n">
-        <v>78480</v>
+        <v>90517</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -26746,21 +26742,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -26773,10 +26769,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>801037</v>
+        <v>801445</v>
       </c>
       <c r="R237" t="n">
-        <v>7496692</v>
+        <v>7496018</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26836,10 +26832,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>117824004</v>
+        <v>117824245</v>
       </c>
       <c r="B238" t="n">
-        <v>78480</v>
+        <v>90517</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -26852,21 +26848,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -26879,10 +26875,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>801445</v>
+        <v>801237</v>
       </c>
       <c r="R238" t="n">
-        <v>7496018</v>
+        <v>7496799</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -26915,11 +26911,6 @@
       <c r="AA238" t="inlineStr">
         <is>
           <t>2024-06-16</t>
-        </is>
-      </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>Rikligt draperade granar</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -26947,10 +26938,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>117824182</v>
+        <v>117823891</v>
       </c>
       <c r="B239" t="n">
-        <v>90517</v>
+        <v>90499</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -26963,21 +26954,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -26990,10 +26981,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>801234</v>
+        <v>800994</v>
       </c>
       <c r="R239" t="n">
-        <v>7496578</v>
+        <v>7496425</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -27053,7 +27044,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>117824123</v>
+        <v>117823893</v>
       </c>
       <c r="B240" t="n">
         <v>90782</v>
@@ -27096,10 +27087,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>801408</v>
+        <v>800994</v>
       </c>
       <c r="R240" t="n">
-        <v>7496150</v>
+        <v>7496425</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27159,10 +27150,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>117824177</v>
+        <v>117824190</v>
       </c>
       <c r="B241" t="n">
-        <v>90852</v>
+        <v>90517</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -27171,25 +27162,25 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>1506</v>
+        <v>5432</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27202,10 +27193,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>801234</v>
+        <v>801226</v>
       </c>
       <c r="R241" t="n">
-        <v>7496578</v>
+        <v>7496690</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27265,10 +27256,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>117823874</v>
+        <v>117823972</v>
       </c>
       <c r="B242" t="n">
-        <v>90499</v>
+        <v>91064</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -27277,25 +27268,25 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -27308,10 +27299,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>800985</v>
+        <v>801391</v>
       </c>
       <c r="R242" t="n">
-        <v>7496417</v>
+        <v>7496026</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27371,10 +27362,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>117824245</v>
+        <v>117824160</v>
       </c>
       <c r="B243" t="n">
-        <v>90517</v>
+        <v>90852</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -27383,25 +27374,25 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -27414,10 +27405,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>801237</v>
+        <v>801351</v>
       </c>
       <c r="R243" t="n">
-        <v>7496799</v>
+        <v>7496276</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27477,10 +27468,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>117824142</v>
+        <v>117823850</v>
       </c>
       <c r="B244" t="n">
-        <v>90517</v>
+        <v>78562</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -27493,21 +27484,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -27520,10 +27511,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>801377</v>
+        <v>801035</v>
       </c>
       <c r="R244" t="n">
-        <v>7496244</v>
+        <v>7496536</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -27583,10 +27574,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>117823842</v>
+        <v>117824223</v>
       </c>
       <c r="B245" t="n">
-        <v>90517</v>
+        <v>56499</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -27595,30 +27586,43 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
@@ -27626,10 +27630,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>801035</v>
+        <v>801211</v>
       </c>
       <c r="R245" t="n">
-        <v>7496536</v>
+        <v>7496750</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -27670,7 +27674,6 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
-      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
@@ -27689,10 +27692,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>117823815</v>
+        <v>117823930</v>
       </c>
       <c r="B246" t="n">
-        <v>56499</v>
+        <v>57436</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -27701,25 +27704,25 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100138</v>
+        <v>103022</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -27728,11 +27731,7 @@
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L246" t="inlineStr"/>
       <c r="M246" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -27745,10 +27744,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>801037</v>
+        <v>801237</v>
       </c>
       <c r="R246" t="n">
-        <v>7496692</v>
+        <v>7496086</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -27807,10 +27806,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>117823930</v>
+        <v>117823690</v>
       </c>
       <c r="B247" t="n">
-        <v>57436</v>
+        <v>57287</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -27823,33 +27822,29 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>103022</v>
+        <v>100109</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr"/>
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr"/>
       <c r="M247" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N247" t="inlineStr"/>
@@ -27859,10 +27854,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>801237</v>
+        <v>801141</v>
       </c>
       <c r="R247" t="n">
-        <v>7496086</v>
+        <v>7496945</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -27895,6 +27890,11 @@
       <c r="AA247" t="inlineStr">
         <is>
           <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -27921,7 +27921,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>117823999</v>
+        <v>117823771</v>
       </c>
       <c r="B248" t="n">
         <v>90517</v>
@@ -27964,10 +27964,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>801445</v>
+        <v>801053</v>
       </c>
       <c r="R248" t="n">
-        <v>7496018</v>
+        <v>7496754</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28027,10 +28027,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>117824190</v>
+        <v>117824123</v>
       </c>
       <c r="B249" t="n">
-        <v>90517</v>
+        <v>90782</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -28043,21 +28043,21 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -28070,10 +28070,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>801226</v>
+        <v>801408</v>
       </c>
       <c r="R249" t="n">
-        <v>7496690</v>
+        <v>7496150</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28133,7 +28133,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>117824223</v>
+        <v>117823815</v>
       </c>
       <c r="B250" t="n">
         <v>56499</v>
@@ -28189,10 +28189,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>801211</v>
+        <v>801037</v>
       </c>
       <c r="R250" t="n">
-        <v>7496750</v>
+        <v>7496692</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28251,10 +28251,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>117824106</v>
+        <v>117824164</v>
       </c>
       <c r="B251" t="n">
-        <v>90782</v>
+        <v>90517</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -28267,21 +28267,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -28294,10 +28294,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>801446</v>
+        <v>801351</v>
       </c>
       <c r="R251" t="n">
-        <v>7496138</v>
+        <v>7496276</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -28357,7 +28357,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>117824025</v>
+        <v>117823827</v>
       </c>
       <c r="B252" t="n">
         <v>90517</v>
@@ -28400,10 +28400,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>801459</v>
+        <v>801032</v>
       </c>
       <c r="R252" t="n">
-        <v>7496022</v>
+        <v>7496586</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28463,10 +28463,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>117823716</v>
+        <v>117823798</v>
       </c>
       <c r="B253" t="n">
-        <v>78480</v>
+        <v>90782</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -28479,21 +28479,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28506,10 +28506,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>801141</v>
+        <v>801037</v>
       </c>
       <c r="R253" t="n">
-        <v>7496945</v>
+        <v>7496692</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28569,10 +28569,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>117823850</v>
+        <v>117824106</v>
       </c>
       <c r="B254" t="n">
-        <v>78562</v>
+        <v>90782</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -28585,21 +28585,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -28612,10 +28612,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>801035</v>
+        <v>801446</v>
       </c>
       <c r="R254" t="n">
-        <v>7496536</v>
+        <v>7496138</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28675,10 +28675,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>117823893</v>
+        <v>117823789</v>
       </c>
       <c r="B255" t="n">
-        <v>90782</v>
+        <v>90517</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -28691,21 +28691,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -28718,10 +28718,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>800994</v>
+        <v>801037</v>
       </c>
       <c r="R255" t="n">
-        <v>7496425</v>
+        <v>7496692</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -20265,10 +20265,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>117493950</v>
+        <v>117494044</v>
       </c>
       <c r="B177" t="n">
-        <v>90782</v>
+        <v>90519</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20281,21 +20281,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -20308,10 +20308,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>801270</v>
+        <v>801235</v>
       </c>
       <c r="R177" t="n">
-        <v>7496960</v>
+        <v>7497122</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20371,10 +20371,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>117493440</v>
+        <v>117493818</v>
       </c>
       <c r="B178" t="n">
-        <v>90517</v>
+        <v>90784</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20387,21 +20387,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -20414,10 +20414,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>801417</v>
+        <v>801529</v>
       </c>
       <c r="R178" t="n">
-        <v>7497205</v>
+        <v>7496739</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20477,10 +20477,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>117493790</v>
+        <v>117493766</v>
       </c>
       <c r="B179" t="n">
-        <v>57303</v>
+        <v>78482</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20493,31 +20493,26 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
@@ -20525,10 +20520,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>801649</v>
+        <v>801686</v>
       </c>
       <c r="R179" t="n">
-        <v>7496917</v>
+        <v>7496943</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20563,17 +20558,13 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>Skalad björk</t>
-        </is>
-      </c>
       <c r="AD179" t="b">
         <v>0</v>
       </c>
       <c r="AE179" t="b">
         <v>0</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
@@ -20592,10 +20583,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>117493421</v>
+        <v>117493964</v>
       </c>
       <c r="B180" t="n">
-        <v>57656</v>
+        <v>90784</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20604,54 +20595,41 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>103015</v>
+        <v>658</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>801393</v>
+        <v>801235</v>
       </c>
       <c r="R180" t="n">
-        <v>7497245</v>
+        <v>7496982</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20692,6 +20670,7 @@
       <c r="AE180" t="b">
         <v>0</v>
       </c>
+      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
@@ -20710,10 +20689,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>117493814</v>
+        <v>117493583</v>
       </c>
       <c r="B181" t="n">
-        <v>90688</v>
+        <v>90515</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20722,25 +20701,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>48</v>
+        <v>1204</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20753,10 +20732,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>801529</v>
+        <v>801555</v>
       </c>
       <c r="R181" t="n">
-        <v>7496739</v>
+        <v>7497160</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20816,10 +20795,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>117493718</v>
+        <v>117493790</v>
       </c>
       <c r="B182" t="n">
-        <v>90782</v>
+        <v>57304</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20832,26 +20811,31 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
@@ -20859,10 +20843,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>801713</v>
+        <v>801649</v>
       </c>
       <c r="R182" t="n">
-        <v>7497045</v>
+        <v>7496917</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20897,13 +20881,17 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Skalad björk</t>
+        </is>
+      </c>
       <c r="AD182" t="b">
         <v>0</v>
       </c>
       <c r="AE182" t="b">
         <v>0</v>
       </c>
-      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
@@ -20922,10 +20910,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>117493495</v>
+        <v>117493800</v>
       </c>
       <c r="B183" t="n">
-        <v>90782</v>
+        <v>90519</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20938,21 +20926,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20965,10 +20953,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>801505</v>
+        <v>801538</v>
       </c>
       <c r="R183" t="n">
-        <v>7497188</v>
+        <v>7496766</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21028,10 +21016,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>117494135</v>
+        <v>117493978</v>
       </c>
       <c r="B184" t="n">
-        <v>57303</v>
+        <v>90519</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21044,31 +21032,26 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
@@ -21076,10 +21059,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>801271</v>
+        <v>801204</v>
       </c>
       <c r="R184" t="n">
-        <v>7497120</v>
+        <v>7497033</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21114,17 +21097,13 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>Stort hål hackad i torrgran, möjligtvis ett boträd</t>
-        </is>
-      </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
       <c r="AE184" t="b">
         <v>0</v>
       </c>
+      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
@@ -21143,10 +21122,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>117493490</v>
+        <v>117493561</v>
       </c>
       <c r="B185" t="n">
-        <v>90495</v>
+        <v>90519</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21159,21 +21138,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -21186,10 +21165,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>801505</v>
+        <v>801519</v>
       </c>
       <c r="R185" t="n">
-        <v>7497188</v>
+        <v>7497181</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21249,10 +21228,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>117493545</v>
+        <v>117493725</v>
       </c>
       <c r="B186" t="n">
-        <v>56491</v>
+        <v>90690</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21261,39 +21240,30 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>102612</v>
+        <v>48</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
@@ -21301,10 +21271,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>801515</v>
+        <v>801713</v>
       </c>
       <c r="R186" t="n">
-        <v>7497168</v>
+        <v>7497045</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21345,6 +21315,7 @@
       <c r="AE186" t="b">
         <v>0</v>
       </c>
+      <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
       </c>
@@ -21363,10 +21334,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>117493966</v>
+        <v>117493541</v>
       </c>
       <c r="B187" t="n">
-        <v>90499</v>
+        <v>90501</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21406,10 +21377,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>801235</v>
+        <v>801515</v>
       </c>
       <c r="R187" t="n">
-        <v>7496982</v>
+        <v>7497168</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21469,10 +21440,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>117493465</v>
+        <v>117493924</v>
       </c>
       <c r="B188" t="n">
-        <v>90517</v>
+        <v>90690</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21481,25 +21452,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>5432</v>
+        <v>48</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -21512,10 +21483,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>801438</v>
+        <v>801276</v>
       </c>
       <c r="R188" t="n">
-        <v>7497203</v>
+        <v>7496938</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21575,10 +21546,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>117493749</v>
+        <v>117493500</v>
       </c>
       <c r="B189" t="n">
-        <v>57287</v>
+        <v>90501</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21591,31 +21562,26 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
@@ -21623,10 +21589,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>801713</v>
+        <v>801505</v>
       </c>
       <c r="R189" t="n">
-        <v>7497045</v>
+        <v>7497188</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21661,17 +21627,13 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD189" t="b">
         <v>0</v>
       </c>
       <c r="AE189" t="b">
         <v>0</v>
       </c>
+      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
@@ -21690,10 +21652,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>117493541</v>
+        <v>117493930</v>
       </c>
       <c r="B190" t="n">
-        <v>90499</v>
+        <v>90466</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21702,25 +21664,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21733,10 +21695,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>801515</v>
+        <v>801276</v>
       </c>
       <c r="R190" t="n">
-        <v>7497168</v>
+        <v>7496938</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21799,7 +21761,7 @@
         <v>117494050</v>
       </c>
       <c r="B191" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -21902,10 +21864,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>117493818</v>
+        <v>117493849</v>
       </c>
       <c r="B192" t="n">
-        <v>90782</v>
+        <v>57288</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -21918,26 +21880,31 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
@@ -21983,13 +21950,17 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Mindre gran skalad på bark i små bitar som låg runt på marken.</t>
+        </is>
+      </c>
       <c r="AD192" t="b">
         <v>0</v>
       </c>
       <c r="AE192" t="b">
         <v>0</v>
       </c>
-      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
@@ -22008,10 +21979,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>117493766</v>
+        <v>117493892</v>
       </c>
       <c r="B193" t="n">
-        <v>78480</v>
+        <v>90519</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22024,21 +21995,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -22051,10 +22022,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>801686</v>
+        <v>801386</v>
       </c>
       <c r="R193" t="n">
-        <v>7496943</v>
+        <v>7496874</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22114,10 +22085,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>117493800</v>
+        <v>117493446</v>
       </c>
       <c r="B194" t="n">
-        <v>90517</v>
+        <v>78482</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22130,21 +22101,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -22157,10 +22128,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>801538</v>
+        <v>801417</v>
       </c>
       <c r="R194" t="n">
-        <v>7496766</v>
+        <v>7497205</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22220,10 +22191,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>117493585</v>
+        <v>117493495</v>
       </c>
       <c r="B195" t="n">
-        <v>78480</v>
+        <v>90784</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22236,21 +22207,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -22263,10 +22234,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>801555</v>
+        <v>801505</v>
       </c>
       <c r="R195" t="n">
-        <v>7497160</v>
+        <v>7497188</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22326,10 +22297,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>117493892</v>
+        <v>117493585</v>
       </c>
       <c r="B196" t="n">
-        <v>90517</v>
+        <v>78482</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22342,21 +22313,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -22369,10 +22340,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>801386</v>
+        <v>801555</v>
       </c>
       <c r="R196" t="n">
-        <v>7496874</v>
+        <v>7497160</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22432,10 +22403,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>117493964</v>
+        <v>117493571</v>
       </c>
       <c r="B197" t="n">
-        <v>90782</v>
+        <v>78482</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22448,21 +22419,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -22475,10 +22446,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>801235</v>
+        <v>801551</v>
       </c>
       <c r="R197" t="n">
-        <v>7496982</v>
+        <v>7497149</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22538,10 +22509,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>117493906</v>
+        <v>117493950</v>
       </c>
       <c r="B198" t="n">
-        <v>78480</v>
+        <v>90784</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22554,21 +22525,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -22581,10 +22552,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>801379</v>
+        <v>801270</v>
       </c>
       <c r="R198" t="n">
-        <v>7496877</v>
+        <v>7496960</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22644,10 +22615,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>117494153</v>
+        <v>117493749</v>
       </c>
       <c r="B199" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22660,26 +22631,31 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
@@ -22687,10 +22663,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>801294</v>
+        <v>801713</v>
       </c>
       <c r="R199" t="n">
-        <v>7497230</v>
+        <v>7497045</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22725,13 +22701,17 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD199" t="b">
         <v>0</v>
       </c>
       <c r="AE199" t="b">
         <v>0</v>
       </c>
-      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
@@ -22750,10 +22730,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>117493978</v>
+        <v>117494153</v>
       </c>
       <c r="B200" t="n">
-        <v>90517</v>
+        <v>90519</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22793,10 +22773,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>801204</v>
+        <v>801294</v>
       </c>
       <c r="R200" t="n">
-        <v>7497033</v>
+        <v>7497230</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22856,10 +22836,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>117493571</v>
+        <v>117493490</v>
       </c>
       <c r="B201" t="n">
-        <v>78480</v>
+        <v>90497</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22872,21 +22852,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -22899,10 +22879,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>801551</v>
+        <v>801505</v>
       </c>
       <c r="R201" t="n">
-        <v>7497149</v>
+        <v>7497188</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22962,10 +22942,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>117493927</v>
+        <v>117493440</v>
       </c>
       <c r="B202" t="n">
-        <v>90782</v>
+        <v>90519</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22978,21 +22958,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -23005,10 +22985,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>801276</v>
+        <v>801417</v>
       </c>
       <c r="R202" t="n">
-        <v>7496938</v>
+        <v>7497205</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -23068,10 +23048,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>117494041</v>
+        <v>117493465</v>
       </c>
       <c r="B203" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23084,31 +23064,26 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
@@ -23116,10 +23091,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>801235</v>
+        <v>801438</v>
       </c>
       <c r="R203" t="n">
-        <v>7497122</v>
+        <v>7497203</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23154,17 +23129,13 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>Gran skalad på små barkflagor och dessa låg runt på marken.</t>
-        </is>
-      </c>
       <c r="AD203" t="b">
         <v>0</v>
       </c>
       <c r="AE203" t="b">
         <v>0</v>
       </c>
+      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
@@ -23183,10 +23154,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>117493849</v>
+        <v>117493966</v>
       </c>
       <c r="B204" t="n">
-        <v>57287</v>
+        <v>90501</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23199,31 +23170,26 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
@@ -23231,10 +23197,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>801529</v>
+        <v>801235</v>
       </c>
       <c r="R204" t="n">
-        <v>7496739</v>
+        <v>7496982</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23269,17 +23235,13 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>Mindre gran skalad på bark i små bitar som låg runt på marken.</t>
-        </is>
-      </c>
       <c r="AD204" t="b">
         <v>0</v>
       </c>
       <c r="AE204" t="b">
         <v>0</v>
       </c>
+      <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="b">
         <v>0</v>
       </c>
@@ -23298,10 +23260,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>117493500</v>
+        <v>117494135</v>
       </c>
       <c r="B205" t="n">
-        <v>90499</v>
+        <v>57304</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23314,26 +23276,31 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
@@ -23341,10 +23308,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>801505</v>
+        <v>801271</v>
       </c>
       <c r="R205" t="n">
-        <v>7497188</v>
+        <v>7497120</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23379,13 +23346,17 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>Stort hål hackad i torrgran, möjligtvis ett boträd</t>
+        </is>
+      </c>
       <c r="AD205" t="b">
         <v>0</v>
       </c>
       <c r="AE205" t="b">
         <v>0</v>
       </c>
-      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
@@ -23404,10 +23375,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>117493446</v>
+        <v>117493545</v>
       </c>
       <c r="B206" t="n">
-        <v>78480</v>
+        <v>56492</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23420,26 +23391,35 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
@@ -23447,10 +23427,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>801417</v>
+        <v>801515</v>
       </c>
       <c r="R206" t="n">
-        <v>7497205</v>
+        <v>7497168</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23491,7 +23471,6 @@
       <c r="AE206" t="b">
         <v>0</v>
       </c>
-      <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="b">
         <v>0</v>
       </c>
@@ -23510,10 +23489,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>117493930</v>
+        <v>117493718</v>
       </c>
       <c r="B207" t="n">
-        <v>90464</v>
+        <v>90784</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23522,25 +23501,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -23553,10 +23532,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>801276</v>
+        <v>801713</v>
       </c>
       <c r="R207" t="n">
-        <v>7496938</v>
+        <v>7497045</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23616,10 +23595,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>117494044</v>
+        <v>117493927</v>
       </c>
       <c r="B208" t="n">
-        <v>90517</v>
+        <v>90784</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -23632,21 +23611,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23659,10 +23638,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>801235</v>
+        <v>801276</v>
       </c>
       <c r="R208" t="n">
-        <v>7497122</v>
+        <v>7496938</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23722,10 +23701,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>117493725</v>
+        <v>117494041</v>
       </c>
       <c r="B209" t="n">
-        <v>90688</v>
+        <v>57288</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -23734,30 +23713,35 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
@@ -23765,10 +23749,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>801713</v>
+        <v>801235</v>
       </c>
       <c r="R209" t="n">
-        <v>7497045</v>
+        <v>7497122</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23803,13 +23787,17 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Gran skalad på små barkflagor och dessa låg runt på marken.</t>
+        </is>
+      </c>
       <c r="AD209" t="b">
         <v>0</v>
       </c>
       <c r="AE209" t="b">
         <v>0</v>
       </c>
-      <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="b">
         <v>0</v>
       </c>
@@ -23828,10 +23816,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>117493561</v>
+        <v>117493531</v>
       </c>
       <c r="B210" t="n">
-        <v>90517</v>
+        <v>90784</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23844,21 +23832,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23871,10 +23859,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>801519</v>
+        <v>801515</v>
       </c>
       <c r="R210" t="n">
-        <v>7497181</v>
+        <v>7497168</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23934,10 +23922,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>117493583</v>
+        <v>117493906</v>
       </c>
       <c r="B211" t="n">
-        <v>90513</v>
+        <v>78482</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -23950,21 +23938,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23977,10 +23965,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>801555</v>
+        <v>801379</v>
       </c>
       <c r="R211" t="n">
-        <v>7497160</v>
+        <v>7496877</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -24040,10 +24028,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>117493924</v>
+        <v>117493814</v>
       </c>
       <c r="B212" t="n">
-        <v>90688</v>
+        <v>90690</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -24083,10 +24071,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>801276</v>
+        <v>801529</v>
       </c>
       <c r="R212" t="n">
-        <v>7496938</v>
+        <v>7496739</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24146,10 +24134,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>117493531</v>
+        <v>117493421</v>
       </c>
       <c r="B213" t="n">
-        <v>90782</v>
+        <v>57657</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24158,41 +24146,54 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P213" t="inlineStr">
         <is>
           <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>801515</v>
+        <v>801393</v>
       </c>
       <c r="R213" t="n">
-        <v>7497168</v>
+        <v>7497245</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -24233,7 +24234,6 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
-      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
@@ -24252,10 +24252,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>117823915</v>
+        <v>117824164</v>
       </c>
       <c r="B214" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24268,31 +24268,26 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
@@ -24300,10 +24295,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>800952</v>
+        <v>801351</v>
       </c>
       <c r="R214" t="n">
-        <v>7496369</v>
+        <v>7496276</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24338,17 +24333,13 @@
           <t>2024-06-16</t>
         </is>
       </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD214" t="b">
         <v>0</v>
       </c>
       <c r="AE214" t="b">
         <v>0</v>
       </c>
+      <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
       </c>
@@ -24367,10 +24358,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>117824142</v>
+        <v>117823999</v>
       </c>
       <c r="B215" t="n">
-        <v>90517</v>
+        <v>90519</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24410,10 +24401,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>801377</v>
+        <v>801445</v>
       </c>
       <c r="R215" t="n">
-        <v>7496244</v>
+        <v>7496018</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24473,10 +24464,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>117823805</v>
+        <v>117824201</v>
       </c>
       <c r="B216" t="n">
-        <v>78480</v>
+        <v>90519</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24489,21 +24480,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -24516,10 +24507,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>801037</v>
+        <v>801211</v>
       </c>
       <c r="R216" t="n">
-        <v>7496692</v>
+        <v>7496750</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24579,10 +24570,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>117824122</v>
+        <v>117824147</v>
       </c>
       <c r="B217" t="n">
-        <v>90941</v>
+        <v>57288</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24591,30 +24582,35 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
@@ -24622,10 +24618,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>801408</v>
+        <v>801377</v>
       </c>
       <c r="R217" t="n">
-        <v>7496150</v>
+        <v>7496244</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24660,13 +24656,17 @@
           <t>2024-06-16</t>
         </is>
       </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>Ringhackning på björk</t>
+        </is>
+      </c>
       <c r="AD217" t="b">
         <v>0</v>
       </c>
       <c r="AE217" t="b">
         <v>0</v>
       </c>
-      <c r="AF217" t="inlineStr"/>
       <c r="AG217" t="b">
         <v>0</v>
       </c>
@@ -24685,10 +24685,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>117824279</v>
+        <v>117823842</v>
       </c>
       <c r="B218" t="n">
-        <v>90517</v>
+        <v>90519</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24728,10 +24728,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>801279</v>
+        <v>801035</v>
       </c>
       <c r="R218" t="n">
-        <v>7496824</v>
+        <v>7496536</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24791,10 +24791,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>117824182</v>
+        <v>117823937</v>
       </c>
       <c r="B219" t="n">
-        <v>90517</v>
+        <v>90784</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24807,21 +24807,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -24834,10 +24834,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>801234</v>
+        <v>801280</v>
       </c>
       <c r="R219" t="n">
-        <v>7496578</v>
+        <v>7496066</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24897,10 +24897,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>117824177</v>
+        <v>117823789</v>
       </c>
       <c r="B220" t="n">
-        <v>90852</v>
+        <v>90519</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -24909,25 +24909,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1506</v>
+        <v>5432</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -24940,10 +24940,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>801234</v>
+        <v>801037</v>
       </c>
       <c r="R220" t="n">
-        <v>7496578</v>
+        <v>7496692</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25003,10 +25003,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>117824004</v>
+        <v>117824190</v>
       </c>
       <c r="B221" t="n">
-        <v>78480</v>
+        <v>90519</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -25019,21 +25019,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -25046,10 +25046,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>801445</v>
+        <v>801226</v>
       </c>
       <c r="R221" t="n">
-        <v>7496018</v>
+        <v>7496690</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25082,11 +25082,6 @@
       <c r="AA221" t="inlineStr">
         <is>
           <t>2024-06-16</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>Rikligt draperade granar</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -25114,10 +25109,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>117823847</v>
+        <v>117824245</v>
       </c>
       <c r="B222" t="n">
-        <v>78480</v>
+        <v>90519</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -25130,21 +25125,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -25157,10 +25152,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>801035</v>
+        <v>801237</v>
       </c>
       <c r="R222" t="n">
-        <v>7496536</v>
+        <v>7496799</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25220,10 +25215,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>117823881</v>
+        <v>117823794</v>
       </c>
       <c r="B223" t="n">
-        <v>78480</v>
+        <v>90690</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -25232,25 +25227,25 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>48</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -25263,10 +25258,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>800985</v>
+        <v>801037</v>
       </c>
       <c r="R223" t="n">
-        <v>7496417</v>
+        <v>7496692</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25326,10 +25321,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>117824201</v>
+        <v>117823827</v>
       </c>
       <c r="B224" t="n">
-        <v>90517</v>
+        <v>90519</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -25369,10 +25364,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>801211</v>
+        <v>801032</v>
       </c>
       <c r="R224" t="n">
-        <v>7496750</v>
+        <v>7496586</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25432,10 +25427,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>117823862</v>
+        <v>117823972</v>
       </c>
       <c r="B225" t="n">
-        <v>90517</v>
+        <v>91066</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -25444,25 +25439,25 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -25475,10 +25470,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>801027</v>
+        <v>801391</v>
       </c>
       <c r="R225" t="n">
-        <v>7496436</v>
+        <v>7496026</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25538,10 +25533,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>117823716</v>
+        <v>117824223</v>
       </c>
       <c r="B226" t="n">
-        <v>78480</v>
+        <v>56500</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -25550,30 +25545,43 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
@@ -25581,10 +25589,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>801141</v>
+        <v>801211</v>
       </c>
       <c r="R226" t="n">
-        <v>7496945</v>
+        <v>7496750</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25625,7 +25633,6 @@
       <c r="AE226" t="b">
         <v>0</v>
       </c>
-      <c r="AF226" t="inlineStr"/>
       <c r="AG226" t="b">
         <v>0</v>
       </c>
@@ -25644,10 +25651,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>117823874</v>
+        <v>117823690</v>
       </c>
       <c r="B227" t="n">
-        <v>90499</v>
+        <v>57288</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -25660,26 +25667,31 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
@@ -25687,10 +25699,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>800985</v>
+        <v>801141</v>
       </c>
       <c r="R227" t="n">
-        <v>7496417</v>
+        <v>7496945</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25725,13 +25737,17 @@
           <t>2024-06-16</t>
         </is>
       </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD227" t="b">
         <v>0</v>
       </c>
       <c r="AE227" t="b">
         <v>0</v>
       </c>
-      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
@@ -25750,10 +25766,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>117823937</v>
+        <v>117823716</v>
       </c>
       <c r="B228" t="n">
-        <v>90782</v>
+        <v>78482</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -25766,21 +25782,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -25793,10 +25809,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>801280</v>
+        <v>801141</v>
       </c>
       <c r="R228" t="n">
-        <v>7496066</v>
+        <v>7496945</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25856,10 +25872,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>117823794</v>
+        <v>117824025</v>
       </c>
       <c r="B229" t="n">
-        <v>90688</v>
+        <v>90519</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -25868,25 +25884,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>48</v>
+        <v>5432</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -25899,10 +25915,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>801037</v>
+        <v>801459</v>
       </c>
       <c r="R229" t="n">
-        <v>7496692</v>
+        <v>7496022</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25962,10 +25978,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>117824025</v>
+        <v>117823862</v>
       </c>
       <c r="B230" t="n">
-        <v>90517</v>
+        <v>90519</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -26005,10 +26021,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>801459</v>
+        <v>801027</v>
       </c>
       <c r="R230" t="n">
-        <v>7496022</v>
+        <v>7496436</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -26068,10 +26084,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>117823981</v>
+        <v>117823798</v>
       </c>
       <c r="B231" t="n">
-        <v>78480</v>
+        <v>90784</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -26084,21 +26100,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -26111,10 +26127,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>801391</v>
+        <v>801037</v>
       </c>
       <c r="R231" t="n">
-        <v>7496026</v>
+        <v>7496692</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26147,11 +26163,6 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2024-06-16</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>Rikligt draperade granar</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26179,10 +26190,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>117824147</v>
+        <v>117823881</v>
       </c>
       <c r="B232" t="n">
-        <v>57287</v>
+        <v>78482</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -26195,31 +26206,26 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
@@ -26227,10 +26233,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>801377</v>
+        <v>800985</v>
       </c>
       <c r="R232" t="n">
-        <v>7496244</v>
+        <v>7496417</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26265,17 +26271,13 @@
           <t>2024-06-16</t>
         </is>
       </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>Ringhackning på björk</t>
-        </is>
-      </c>
       <c r="AD232" t="b">
         <v>0</v>
       </c>
       <c r="AE232" t="b">
         <v>0</v>
       </c>
+      <c r="AF232" t="inlineStr"/>
       <c r="AG232" t="b">
         <v>0</v>
       </c>
@@ -26294,10 +26296,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>117824252</v>
+        <v>117824182</v>
       </c>
       <c r="B233" t="n">
-        <v>57656</v>
+        <v>90519</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -26306,39 +26308,30 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
@@ -26346,10 +26339,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>801237</v>
+        <v>801234</v>
       </c>
       <c r="R233" t="n">
-        <v>7496799</v>
+        <v>7496578</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26390,6 +26383,7 @@
       <c r="AE233" t="b">
         <v>0</v>
       </c>
+      <c r="AF233" t="inlineStr"/>
       <c r="AG233" t="b">
         <v>0</v>
       </c>
@@ -26408,10 +26402,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>117823842</v>
+        <v>117823805</v>
       </c>
       <c r="B234" t="n">
-        <v>90517</v>
+        <v>78482</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -26424,21 +26418,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -26451,10 +26445,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>801035</v>
+        <v>801037</v>
       </c>
       <c r="R234" t="n">
-        <v>7496536</v>
+        <v>7496692</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26514,10 +26508,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>117824022</v>
+        <v>117824160</v>
       </c>
       <c r="B235" t="n">
-        <v>91195</v>
+        <v>90854</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -26530,21 +26524,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>67</v>
+        <v>1506</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -26557,10 +26551,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>801459</v>
+        <v>801351</v>
       </c>
       <c r="R235" t="n">
-        <v>7496022</v>
+        <v>7496276</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -26620,10 +26614,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>117824290</v>
+        <v>117824022</v>
       </c>
       <c r="B236" t="n">
-        <v>90517</v>
+        <v>91197</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -26632,25 +26626,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>5432</v>
+        <v>67</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -26663,10 +26657,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>801321</v>
+        <v>801459</v>
       </c>
       <c r="R236" t="n">
-        <v>7497019</v>
+        <v>7496022</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26726,10 +26720,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>117823999</v>
+        <v>117823915</v>
       </c>
       <c r="B237" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -26742,26 +26736,31 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
@@ -26769,10 +26768,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>801445</v>
+        <v>800952</v>
       </c>
       <c r="R237" t="n">
-        <v>7496018</v>
+        <v>7496369</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26807,13 +26806,17 @@
           <t>2024-06-16</t>
         </is>
       </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD237" t="b">
         <v>0</v>
       </c>
       <c r="AE237" t="b">
         <v>0</v>
       </c>
-      <c r="AF237" t="inlineStr"/>
       <c r="AG237" t="b">
         <v>0</v>
       </c>
@@ -26832,10 +26835,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>117824245</v>
+        <v>117824252</v>
       </c>
       <c r="B238" t="n">
-        <v>90517</v>
+        <v>57657</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -26844,30 +26847,39 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
@@ -26919,7 +26931,6 @@
       <c r="AE238" t="b">
         <v>0</v>
       </c>
-      <c r="AF238" t="inlineStr"/>
       <c r="AG238" t="b">
         <v>0</v>
       </c>
@@ -26938,10 +26949,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>117823891</v>
+        <v>117823874</v>
       </c>
       <c r="B239" t="n">
-        <v>90499</v>
+        <v>90501</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -26981,10 +26992,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>800994</v>
+        <v>800985</v>
       </c>
       <c r="R239" t="n">
-        <v>7496425</v>
+        <v>7496417</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -27044,10 +27055,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>117823893</v>
+        <v>117824004</v>
       </c>
       <c r="B240" t="n">
-        <v>90782</v>
+        <v>78482</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -27060,21 +27071,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -27087,10 +27098,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>800994</v>
+        <v>801445</v>
       </c>
       <c r="R240" t="n">
-        <v>7496425</v>
+        <v>7496018</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27123,6 +27134,11 @@
       <c r="AA240" t="inlineStr">
         <is>
           <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>Rikligt draperade granar</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -27150,10 +27166,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>117824190</v>
+        <v>117824279</v>
       </c>
       <c r="B241" t="n">
-        <v>90517</v>
+        <v>90519</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -27193,10 +27209,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>801226</v>
+        <v>801279</v>
       </c>
       <c r="R241" t="n">
-        <v>7496690</v>
+        <v>7496824</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27256,10 +27272,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>117823972</v>
+        <v>117823930</v>
       </c>
       <c r="B242" t="n">
-        <v>91064</v>
+        <v>57437</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -27268,30 +27284,39 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>760</v>
+        <v>103022</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
@@ -27299,10 +27324,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>801391</v>
+        <v>801237</v>
       </c>
       <c r="R242" t="n">
-        <v>7496026</v>
+        <v>7496086</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27343,7 +27368,6 @@
       <c r="AE242" t="b">
         <v>0</v>
       </c>
-      <c r="AF242" t="inlineStr"/>
       <c r="AG242" t="b">
         <v>0</v>
       </c>
@@ -27362,10 +27386,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>117824160</v>
+        <v>117824122</v>
       </c>
       <c r="B243" t="n">
-        <v>90852</v>
+        <v>90943</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -27378,21 +27402,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>1506</v>
+        <v>1209</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -27405,10 +27429,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>801351</v>
+        <v>801408</v>
       </c>
       <c r="R243" t="n">
-        <v>7496276</v>
+        <v>7496150</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27468,10 +27492,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>117823850</v>
+        <v>117823981</v>
       </c>
       <c r="B244" t="n">
-        <v>78562</v>
+        <v>78482</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -27484,21 +27508,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -27511,10 +27535,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>801035</v>
+        <v>801391</v>
       </c>
       <c r="R244" t="n">
-        <v>7496536</v>
+        <v>7496026</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -27547,6 +27571,11 @@
       <c r="AA244" t="inlineStr">
         <is>
           <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>Rikligt draperade granar</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27574,10 +27603,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>117824223</v>
+        <v>117824290</v>
       </c>
       <c r="B245" t="n">
-        <v>56499</v>
+        <v>90519</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -27586,43 +27615,30 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
@@ -27630,10 +27646,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>801211</v>
+        <v>801321</v>
       </c>
       <c r="R245" t="n">
-        <v>7496750</v>
+        <v>7497019</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -27674,6 +27690,7 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
+      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
@@ -27692,10 +27709,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>117823930</v>
+        <v>117823891</v>
       </c>
       <c r="B246" t="n">
-        <v>57436</v>
+        <v>90501</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -27708,35 +27725,26 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>103022</v>
+        <v>1202</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
@@ -27744,10 +27752,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>801237</v>
+        <v>800994</v>
       </c>
       <c r="R246" t="n">
-        <v>7496086</v>
+        <v>7496425</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -27788,6 +27796,7 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
+      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
@@ -27806,10 +27815,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>117823690</v>
+        <v>117824177</v>
       </c>
       <c r="B247" t="n">
-        <v>57287</v>
+        <v>90854</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -27818,35 +27827,30 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
+      <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
@@ -27854,10 +27858,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>801141</v>
+        <v>801234</v>
       </c>
       <c r="R247" t="n">
-        <v>7496945</v>
+        <v>7496578</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -27892,17 +27896,13 @@
           <t>2024-06-16</t>
         </is>
       </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD247" t="b">
         <v>0</v>
       </c>
       <c r="AE247" t="b">
         <v>0</v>
       </c>
+      <c r="AF247" t="inlineStr"/>
       <c r="AG247" t="b">
         <v>0</v>
       </c>
@@ -27921,10 +27921,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>117823771</v>
+        <v>117823847</v>
       </c>
       <c r="B248" t="n">
-        <v>90517</v>
+        <v>78482</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -27937,21 +27937,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -27964,10 +27964,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>801053</v>
+        <v>801035</v>
       </c>
       <c r="R248" t="n">
-        <v>7496754</v>
+        <v>7496536</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28027,10 +28027,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>117824123</v>
+        <v>117824142</v>
       </c>
       <c r="B249" t="n">
-        <v>90782</v>
+        <v>90519</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -28043,21 +28043,21 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -28070,10 +28070,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>801408</v>
+        <v>801377</v>
       </c>
       <c r="R249" t="n">
-        <v>7496150</v>
+        <v>7496244</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28136,7 +28136,7 @@
         <v>117823815</v>
       </c>
       <c r="B250" t="n">
-        <v>56499</v>
+        <v>56500</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -28251,10 +28251,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>117824164</v>
+        <v>117824123</v>
       </c>
       <c r="B251" t="n">
-        <v>90517</v>
+        <v>90784</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -28267,21 +28267,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -28294,10 +28294,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>801351</v>
+        <v>801408</v>
       </c>
       <c r="R251" t="n">
-        <v>7496276</v>
+        <v>7496150</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -28357,10 +28357,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>117823827</v>
+        <v>117823850</v>
       </c>
       <c r="B252" t="n">
-        <v>90517</v>
+        <v>78564</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -28373,21 +28373,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -28400,10 +28400,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>801032</v>
+        <v>801035</v>
       </c>
       <c r="R252" t="n">
-        <v>7496586</v>
+        <v>7496536</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28463,10 +28463,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>117823798</v>
+        <v>117824106</v>
       </c>
       <c r="B253" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -28506,10 +28506,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>801037</v>
+        <v>801446</v>
       </c>
       <c r="R253" t="n">
-        <v>7496692</v>
+        <v>7496138</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28569,10 +28569,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>117824106</v>
+        <v>117823893</v>
       </c>
       <c r="B254" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -28612,10 +28612,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>801446</v>
+        <v>800994</v>
       </c>
       <c r="R254" t="n">
-        <v>7496138</v>
+        <v>7496425</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28675,10 +28675,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>117823789</v>
+        <v>117823771</v>
       </c>
       <c r="B255" t="n">
-        <v>90517</v>
+        <v>90519</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -28718,10 +28718,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>801037</v>
+        <v>801053</v>
       </c>
       <c r="R255" t="n">
-        <v>7496692</v>
+        <v>7496754</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -22085,10 +22085,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>117493446</v>
+        <v>117493495</v>
       </c>
       <c r="B194" t="n">
-        <v>78482</v>
+        <v>90784</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22101,21 +22101,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -22128,10 +22128,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>801417</v>
+        <v>801505</v>
       </c>
       <c r="R194" t="n">
-        <v>7497205</v>
+        <v>7497188</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22191,10 +22191,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>117493495</v>
+        <v>117493446</v>
       </c>
       <c r="B195" t="n">
-        <v>90784</v>
+        <v>78482</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22207,21 +22207,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -22234,10 +22234,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>801505</v>
+        <v>801417</v>
       </c>
       <c r="R195" t="n">
-        <v>7497188</v>
+        <v>7497205</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22297,10 +22297,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>117493585</v>
+        <v>117493950</v>
       </c>
       <c r="B196" t="n">
-        <v>78482</v>
+        <v>90784</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22313,21 +22313,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -22340,10 +22340,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>801555</v>
+        <v>801270</v>
       </c>
       <c r="R196" t="n">
-        <v>7497160</v>
+        <v>7496960</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22403,7 +22403,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>117493571</v>
+        <v>117493585</v>
       </c>
       <c r="B197" t="n">
         <v>78482</v>
@@ -22446,10 +22446,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>801551</v>
+        <v>801555</v>
       </c>
       <c r="R197" t="n">
-        <v>7497149</v>
+        <v>7497160</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22509,10 +22509,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>117493950</v>
+        <v>117493571</v>
       </c>
       <c r="B198" t="n">
-        <v>90784</v>
+        <v>78482</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22525,21 +22525,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -22552,10 +22552,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>801270</v>
+        <v>801551</v>
       </c>
       <c r="R198" t="n">
-        <v>7496960</v>
+        <v>7497149</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -23701,10 +23701,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>117494041</v>
+        <v>117493531</v>
       </c>
       <c r="B209" t="n">
-        <v>57288</v>
+        <v>90784</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -23717,31 +23717,26 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
@@ -23749,10 +23744,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>801235</v>
+        <v>801515</v>
       </c>
       <c r="R209" t="n">
-        <v>7497122</v>
+        <v>7497168</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23787,17 +23782,13 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>Gran skalad på små barkflagor och dessa låg runt på marken.</t>
-        </is>
-      </c>
       <c r="AD209" t="b">
         <v>0</v>
       </c>
       <c r="AE209" t="b">
         <v>0</v>
       </c>
+      <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="b">
         <v>0</v>
       </c>
@@ -23816,10 +23807,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>117493531</v>
+        <v>117494041</v>
       </c>
       <c r="B210" t="n">
-        <v>90784</v>
+        <v>57288</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23832,26 +23823,31 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
@@ -23859,10 +23855,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>801515</v>
+        <v>801235</v>
       </c>
       <c r="R210" t="n">
-        <v>7497168</v>
+        <v>7497122</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23897,13 +23893,17 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>Gran skalad på små barkflagor och dessa låg runt på marken.</t>
+        </is>
+      </c>
       <c r="AD210" t="b">
         <v>0</v>
       </c>
       <c r="AE210" t="b">
         <v>0</v>
       </c>
-      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY255"/>
+  <dimension ref="A1:AY306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28779,6 +28779,5520 @@
       </c>
       <c r="AY255" t="inlineStr"/>
     </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>118922549</v>
+      </c>
+      <c r="B256" t="n">
+        <v>90522</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr"/>
+      <c r="J256" t="inlineStr"/>
+      <c r="K256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q256" t="n">
+        <v>801498</v>
+      </c>
+      <c r="R256" t="n">
+        <v>7496951</v>
+      </c>
+      <c r="S256" t="n">
+        <v>10</v>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF256" t="inlineStr"/>
+      <c r="AG256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT256" t="inlineStr"/>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>118922573</v>
+      </c>
+      <c r="B257" t="n">
+        <v>79594</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr"/>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>801542</v>
+      </c>
+      <c r="R257" t="n">
+        <v>7496947</v>
+      </c>
+      <c r="S257" t="n">
+        <v>10</v>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF257" t="inlineStr"/>
+      <c r="AG257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT257" t="inlineStr"/>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX257" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>118923038</v>
+      </c>
+      <c r="B258" t="n">
+        <v>91294</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Hericium coralloides</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>801511</v>
+      </c>
+      <c r="R258" t="n">
+        <v>7496775</v>
+      </c>
+      <c r="S258" t="n">
+        <v>10</v>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF258" t="inlineStr"/>
+      <c r="AG258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT258" t="inlineStr"/>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>118923085</v>
+      </c>
+      <c r="B259" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr"/>
+      <c r="J259" t="inlineStr"/>
+      <c r="K259" t="inlineStr"/>
+      <c r="N259" t="inlineStr"/>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q259" t="n">
+        <v>801450</v>
+      </c>
+      <c r="R259" t="n">
+        <v>7496709</v>
+      </c>
+      <c r="S259" t="n">
+        <v>10</v>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF259" t="inlineStr"/>
+      <c r="AG259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT259" t="inlineStr"/>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>118923437</v>
+      </c>
+      <c r="B260" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr"/>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr"/>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q260" t="n">
+        <v>801301</v>
+      </c>
+      <c r="R260" t="n">
+        <v>7496577</v>
+      </c>
+      <c r="S260" t="n">
+        <v>10</v>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT260" t="inlineStr"/>
+      <c r="AW260" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX260" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>118922409</v>
+      </c>
+      <c r="B261" t="n">
+        <v>90858</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q261" t="n">
+        <v>801382</v>
+      </c>
+      <c r="R261" t="n">
+        <v>7497242</v>
+      </c>
+      <c r="S261" t="n">
+        <v>10</v>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF261" t="inlineStr"/>
+      <c r="AG261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT261" t="inlineStr"/>
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>118923452</v>
+      </c>
+      <c r="B262" t="n">
+        <v>90522</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr"/>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q262" t="n">
+        <v>801301</v>
+      </c>
+      <c r="R262" t="n">
+        <v>7496577</v>
+      </c>
+      <c r="S262" t="n">
+        <v>10</v>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF262" t="inlineStr"/>
+      <c r="AG262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT262" t="inlineStr"/>
+      <c r="AW262" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX262" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>118922594</v>
+      </c>
+      <c r="B263" t="n">
+        <v>90504</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr"/>
+      <c r="J263" t="inlineStr"/>
+      <c r="K263" t="inlineStr"/>
+      <c r="N263" t="inlineStr"/>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q263" t="n">
+        <v>801537</v>
+      </c>
+      <c r="R263" t="n">
+        <v>7496912</v>
+      </c>
+      <c r="S263" t="n">
+        <v>10</v>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF263" t="inlineStr"/>
+      <c r="AG263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT263" t="inlineStr"/>
+      <c r="AW263" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX263" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>118923242</v>
+      </c>
+      <c r="B264" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr"/>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr"/>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q264" t="n">
+        <v>801832</v>
+      </c>
+      <c r="R264" t="n">
+        <v>7496176</v>
+      </c>
+      <c r="S264" t="n">
+        <v>10</v>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>Ringhack på mycket grov gran</t>
+        </is>
+      </c>
+      <c r="AD264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT264" t="inlineStr"/>
+      <c r="AW264" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX264" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>118923181</v>
+      </c>
+      <c r="B265" t="n">
+        <v>90899</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q265" t="n">
+        <v>801607</v>
+      </c>
+      <c r="R265" t="n">
+        <v>7496461</v>
+      </c>
+      <c r="S265" t="n">
+        <v>10</v>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD265" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE265" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF265" t="inlineStr"/>
+      <c r="AG265" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT265" t="inlineStr"/>
+      <c r="AW265" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX265" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>118923587</v>
+      </c>
+      <c r="B266" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr"/>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q266" t="n">
+        <v>801360</v>
+      </c>
+      <c r="R266" t="n">
+        <v>7496906</v>
+      </c>
+      <c r="S266" t="n">
+        <v>10</v>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD266" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE266" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG266" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT266" t="inlineStr"/>
+      <c r="AW266" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX266" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>118922492</v>
+      </c>
+      <c r="B267" t="n">
+        <v>90504</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr"/>
+      <c r="J267" t="inlineStr"/>
+      <c r="K267" t="inlineStr"/>
+      <c r="N267" t="inlineStr"/>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q267" t="n">
+        <v>801375</v>
+      </c>
+      <c r="R267" t="n">
+        <v>7497165</v>
+      </c>
+      <c r="S267" t="n">
+        <v>10</v>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF267" t="inlineStr"/>
+      <c r="AG267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT267" t="inlineStr"/>
+      <c r="AW267" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX267" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>118922575</v>
+      </c>
+      <c r="B268" t="n">
+        <v>79600</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr"/>
+      <c r="J268" t="inlineStr"/>
+      <c r="K268" t="inlineStr"/>
+      <c r="N268" t="inlineStr"/>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q268" t="n">
+        <v>801542</v>
+      </c>
+      <c r="R268" t="n">
+        <v>7496947</v>
+      </c>
+      <c r="S268" t="n">
+        <v>10</v>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD268" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE268" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF268" t="inlineStr"/>
+      <c r="AG268" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT268" t="inlineStr"/>
+      <c r="AW268" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX268" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>118923092</v>
+      </c>
+      <c r="B269" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr"/>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr"/>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q269" t="n">
+        <v>801450</v>
+      </c>
+      <c r="R269" t="n">
+        <v>7496709</v>
+      </c>
+      <c r="S269" t="n">
+        <v>10</v>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD269" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE269" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG269" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT269" t="inlineStr"/>
+      <c r="AW269" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX269" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>118923596</v>
+      </c>
+      <c r="B270" t="n">
+        <v>90504</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr"/>
+      <c r="J270" t="inlineStr"/>
+      <c r="K270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q270" t="n">
+        <v>801299</v>
+      </c>
+      <c r="R270" t="n">
+        <v>7496931</v>
+      </c>
+      <c r="S270" t="n">
+        <v>10</v>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD270" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE270" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF270" t="inlineStr"/>
+      <c r="AG270" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT270" t="inlineStr"/>
+      <c r="AW270" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX270" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>118923124</v>
+      </c>
+      <c r="B271" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr"/>
+      <c r="J271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q271" t="n">
+        <v>801606</v>
+      </c>
+      <c r="R271" t="n">
+        <v>7496529</v>
+      </c>
+      <c r="S271" t="n">
+        <v>10</v>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF271" t="inlineStr"/>
+      <c r="AG271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT271" t="inlineStr"/>
+      <c r="AW271" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX271" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>118923466</v>
+      </c>
+      <c r="B272" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr"/>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q272" t="n">
+        <v>801362</v>
+      </c>
+      <c r="R272" t="n">
+        <v>7496605</v>
+      </c>
+      <c r="S272" t="n">
+        <v>10</v>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD272" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE272" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG272" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT272" t="inlineStr"/>
+      <c r="AW272" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX272" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>118923225</v>
+      </c>
+      <c r="B273" t="n">
+        <v>90522</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q273" t="n">
+        <v>801833</v>
+      </c>
+      <c r="R273" t="n">
+        <v>7496271</v>
+      </c>
+      <c r="S273" t="n">
+        <v>10</v>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF273" t="inlineStr"/>
+      <c r="AG273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT273" t="inlineStr"/>
+      <c r="AW273" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX273" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>118923214</v>
+      </c>
+      <c r="B274" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="N274" t="inlineStr"/>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q274" t="n">
+        <v>801782</v>
+      </c>
+      <c r="R274" t="n">
+        <v>7496335</v>
+      </c>
+      <c r="S274" t="n">
+        <v>10</v>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF274" t="inlineStr"/>
+      <c r="AG274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT274" t="inlineStr"/>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>118923059</v>
+      </c>
+      <c r="B275" t="n">
+        <v>57134</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>100096</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Pandion haliaetus</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr"/>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q275" t="n">
+        <v>801503</v>
+      </c>
+      <c r="R275" t="n">
+        <v>7496772</v>
+      </c>
+      <c r="S275" t="n">
+        <v>10</v>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD275" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE275" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG275" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT275" t="inlineStr"/>
+      <c r="AW275" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX275" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>118923112</v>
+      </c>
+      <c r="B276" t="n">
+        <v>90522</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="N276" t="inlineStr"/>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q276" t="n">
+        <v>801607</v>
+      </c>
+      <c r="R276" t="n">
+        <v>7496562</v>
+      </c>
+      <c r="S276" t="n">
+        <v>10</v>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD276" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE276" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF276" t="inlineStr"/>
+      <c r="AG276" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT276" t="inlineStr"/>
+      <c r="AW276" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX276" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>118922552</v>
+      </c>
+      <c r="B277" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q277" t="n">
+        <v>801498</v>
+      </c>
+      <c r="R277" t="n">
+        <v>7496951</v>
+      </c>
+      <c r="S277" t="n">
+        <v>10</v>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF277" t="inlineStr"/>
+      <c r="AG277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT277" t="inlineStr"/>
+      <c r="AW277" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX277" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>118923136</v>
+      </c>
+      <c r="B278" t="n">
+        <v>90522</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="N278" t="inlineStr"/>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q278" t="n">
+        <v>801589</v>
+      </c>
+      <c r="R278" t="n">
+        <v>7496530</v>
+      </c>
+      <c r="S278" t="n">
+        <v>10</v>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF278" t="inlineStr"/>
+      <c r="AG278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT278" t="inlineStr"/>
+      <c r="AW278" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX278" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>118922592</v>
+      </c>
+      <c r="B279" t="n">
+        <v>90500</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q279" t="n">
+        <v>801537</v>
+      </c>
+      <c r="R279" t="n">
+        <v>7496912</v>
+      </c>
+      <c r="S279" t="n">
+        <v>10</v>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF279" t="inlineStr"/>
+      <c r="AG279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT279" t="inlineStr"/>
+      <c r="AW279" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX279" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>118923055</v>
+      </c>
+      <c r="B280" t="n">
+        <v>56635</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr"/>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q280" t="n">
+        <v>801503</v>
+      </c>
+      <c r="R280" t="n">
+        <v>7496772</v>
+      </c>
+      <c r="S280" t="n">
+        <v>10</v>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD280" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE280" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG280" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT280" t="inlineStr"/>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>118923184</v>
+      </c>
+      <c r="B281" t="n">
+        <v>90522</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="N281" t="inlineStr"/>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q281" t="n">
+        <v>801607</v>
+      </c>
+      <c r="R281" t="n">
+        <v>7496461</v>
+      </c>
+      <c r="S281" t="n">
+        <v>10</v>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF281" t="inlineStr"/>
+      <c r="AG281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT281" t="inlineStr"/>
+      <c r="AW281" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX281" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>118923557</v>
+      </c>
+      <c r="B282" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr"/>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr"/>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q282" t="n">
+        <v>801368</v>
+      </c>
+      <c r="R282" t="n">
+        <v>7496734</v>
+      </c>
+      <c r="S282" t="n">
+        <v>10</v>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AC282" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD282" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE282" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG282" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT282" t="inlineStr"/>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>118922436</v>
+      </c>
+      <c r="B283" t="n">
+        <v>90899</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr"/>
+      <c r="J283" t="inlineStr"/>
+      <c r="K283" t="inlineStr"/>
+      <c r="N283" t="inlineStr"/>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q283" t="n">
+        <v>801392</v>
+      </c>
+      <c r="R283" t="n">
+        <v>7497197</v>
+      </c>
+      <c r="S283" t="n">
+        <v>10</v>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF283" t="inlineStr"/>
+      <c r="AG283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT283" t="inlineStr"/>
+      <c r="AW283" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX283" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>118922600</v>
+      </c>
+      <c r="B284" t="n">
+        <v>90847</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr"/>
+      <c r="J284" t="inlineStr"/>
+      <c r="K284" t="inlineStr"/>
+      <c r="N284" t="inlineStr"/>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q284" t="n">
+        <v>801537</v>
+      </c>
+      <c r="R284" t="n">
+        <v>7496912</v>
+      </c>
+      <c r="S284" t="n">
+        <v>10</v>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF284" t="inlineStr"/>
+      <c r="AG284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT284" t="inlineStr"/>
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX284" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>118923219</v>
+      </c>
+      <c r="B285" t="n">
+        <v>90522</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr"/>
+      <c r="J285" t="inlineStr"/>
+      <c r="K285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q285" t="n">
+        <v>801782</v>
+      </c>
+      <c r="R285" t="n">
+        <v>7496335</v>
+      </c>
+      <c r="S285" t="n">
+        <v>10</v>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF285" t="inlineStr"/>
+      <c r="AG285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT285" t="inlineStr"/>
+      <c r="AW285" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX285" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>118922608</v>
+      </c>
+      <c r="B286" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr"/>
+      <c r="J286" t="inlineStr"/>
+      <c r="K286" t="inlineStr"/>
+      <c r="N286" t="inlineStr"/>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q286" t="n">
+        <v>801537</v>
+      </c>
+      <c r="R286" t="n">
+        <v>7496912</v>
+      </c>
+      <c r="S286" t="n">
+        <v>10</v>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF286" t="inlineStr"/>
+      <c r="AG286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT286" t="inlineStr"/>
+      <c r="AW286" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX286" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>118922478</v>
+      </c>
+      <c r="B287" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr"/>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr"/>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q287" t="n">
+        <v>801386</v>
+      </c>
+      <c r="R287" t="n">
+        <v>7497188</v>
+      </c>
+      <c r="S287" t="n">
+        <v>10</v>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AC287" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD287" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE287" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG287" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT287" t="inlineStr"/>
+      <c r="AW287" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>118923305</v>
+      </c>
+      <c r="B288" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr"/>
+      <c r="J288" t="inlineStr"/>
+      <c r="K288" t="inlineStr"/>
+      <c r="N288" t="inlineStr"/>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q288" t="n">
+        <v>801340</v>
+      </c>
+      <c r="R288" t="n">
+        <v>7496538</v>
+      </c>
+      <c r="S288" t="n">
+        <v>10</v>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD288" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE288" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF288" t="inlineStr"/>
+      <c r="AG288" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT288" t="inlineStr"/>
+      <c r="AW288" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX288" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>118923050</v>
+      </c>
+      <c r="B289" t="n">
+        <v>90522</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr"/>
+      <c r="J289" t="inlineStr"/>
+      <c r="K289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q289" t="n">
+        <v>801503</v>
+      </c>
+      <c r="R289" t="n">
+        <v>7496772</v>
+      </c>
+      <c r="S289" t="n">
+        <v>10</v>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y289" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD289" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE289" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF289" t="inlineStr"/>
+      <c r="AG289" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT289" t="inlineStr"/>
+      <c r="AW289" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX289" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>118923258</v>
+      </c>
+      <c r="B290" t="n">
+        <v>90788</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>658</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr"/>
+      <c r="J290" t="inlineStr"/>
+      <c r="K290" t="inlineStr"/>
+      <c r="N290" t="inlineStr"/>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q290" t="n">
+        <v>801776</v>
+      </c>
+      <c r="R290" t="n">
+        <v>7496263</v>
+      </c>
+      <c r="S290" t="n">
+        <v>10</v>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y290" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD290" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE290" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF290" t="inlineStr"/>
+      <c r="AG290" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT290" t="inlineStr"/>
+      <c r="AW290" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX290" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>118923567</v>
+      </c>
+      <c r="B291" t="n">
+        <v>90522</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr"/>
+      <c r="J291" t="inlineStr"/>
+      <c r="K291" t="inlineStr"/>
+      <c r="N291" t="inlineStr"/>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q291" t="n">
+        <v>801380</v>
+      </c>
+      <c r="R291" t="n">
+        <v>7496726</v>
+      </c>
+      <c r="S291" t="n">
+        <v>10</v>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W291" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y291" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD291" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE291" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF291" t="inlineStr"/>
+      <c r="AG291" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT291" t="inlineStr"/>
+      <c r="AW291" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX291" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>118923132</v>
+      </c>
+      <c r="B292" t="n">
+        <v>90504</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr"/>
+      <c r="J292" t="inlineStr"/>
+      <c r="K292" t="inlineStr"/>
+      <c r="N292" t="inlineStr"/>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q292" t="n">
+        <v>801589</v>
+      </c>
+      <c r="R292" t="n">
+        <v>7496530</v>
+      </c>
+      <c r="S292" t="n">
+        <v>10</v>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W292" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y292" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD292" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE292" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF292" t="inlineStr"/>
+      <c r="AG292" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT292" t="inlineStr"/>
+      <c r="AW292" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX292" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>118923100</v>
+      </c>
+      <c r="B293" t="n">
+        <v>90522</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr"/>
+      <c r="J293" t="inlineStr"/>
+      <c r="K293" t="inlineStr"/>
+      <c r="N293" t="inlineStr"/>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q293" t="n">
+        <v>801455</v>
+      </c>
+      <c r="R293" t="n">
+        <v>7496698</v>
+      </c>
+      <c r="S293" t="n">
+        <v>10</v>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y293" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD293" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE293" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF293" t="inlineStr"/>
+      <c r="AG293" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT293" t="inlineStr"/>
+      <c r="AW293" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX293" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>118923075</v>
+      </c>
+      <c r="B294" t="n">
+        <v>90522</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr"/>
+      <c r="J294" t="inlineStr"/>
+      <c r="K294" t="inlineStr"/>
+      <c r="N294" t="inlineStr"/>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q294" t="n">
+        <v>801454</v>
+      </c>
+      <c r="R294" t="n">
+        <v>7496759</v>
+      </c>
+      <c r="S294" t="n">
+        <v>10</v>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W294" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y294" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD294" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE294" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF294" t="inlineStr"/>
+      <c r="AG294" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT294" t="inlineStr"/>
+      <c r="AW294" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX294" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>118922505</v>
+      </c>
+      <c r="B295" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr"/>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr"/>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q295" t="n">
+        <v>801406</v>
+      </c>
+      <c r="R295" t="n">
+        <v>7497090</v>
+      </c>
+      <c r="S295" t="n">
+        <v>10</v>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W295" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y295" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AC295" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD295" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE295" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG295" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT295" t="inlineStr"/>
+      <c r="AW295" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX295" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>118922489</v>
+      </c>
+      <c r="B296" t="n">
+        <v>90788</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>658</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr"/>
+      <c r="J296" t="inlineStr"/>
+      <c r="K296" t="inlineStr"/>
+      <c r="N296" t="inlineStr"/>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q296" t="n">
+        <v>801375</v>
+      </c>
+      <c r="R296" t="n">
+        <v>7497165</v>
+      </c>
+      <c r="S296" t="n">
+        <v>10</v>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W296" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y296" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD296" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE296" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF296" t="inlineStr"/>
+      <c r="AG296" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT296" t="inlineStr"/>
+      <c r="AW296" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX296" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>118923531</v>
+      </c>
+      <c r="B297" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr"/>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr"/>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q297" t="n">
+        <v>801373</v>
+      </c>
+      <c r="R297" t="n">
+        <v>7496663</v>
+      </c>
+      <c r="S297" t="n">
+        <v>10</v>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W297" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y297" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD297" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE297" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG297" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT297" t="inlineStr"/>
+      <c r="AW297" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX297" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>118923616</v>
+      </c>
+      <c r="B298" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr"/>
+      <c r="J298" t="inlineStr"/>
+      <c r="K298" t="inlineStr"/>
+      <c r="N298" t="inlineStr"/>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q298" t="n">
+        <v>801355</v>
+      </c>
+      <c r="R298" t="n">
+        <v>7497040</v>
+      </c>
+      <c r="S298" t="n">
+        <v>10</v>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W298" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD298" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE298" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF298" t="inlineStr"/>
+      <c r="AG298" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT298" t="inlineStr"/>
+      <c r="AW298" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX298" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>118922367</v>
+      </c>
+      <c r="B299" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr"/>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr"/>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q299" t="n">
+        <v>801313</v>
+      </c>
+      <c r="R299" t="n">
+        <v>7497257</v>
+      </c>
+      <c r="S299" t="n">
+        <v>10</v>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W299" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y299" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AC299" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD299" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE299" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG299" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT299" t="inlineStr"/>
+      <c r="AW299" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX299" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>118922460</v>
+      </c>
+      <c r="B300" t="n">
+        <v>90522</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr"/>
+      <c r="J300" t="inlineStr"/>
+      <c r="K300" t="inlineStr"/>
+      <c r="N300" t="inlineStr"/>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q300" t="n">
+        <v>801386</v>
+      </c>
+      <c r="R300" t="n">
+        <v>7497188</v>
+      </c>
+      <c r="S300" t="n">
+        <v>10</v>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W300" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y300" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD300" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE300" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF300" t="inlineStr"/>
+      <c r="AG300" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT300" t="inlineStr"/>
+      <c r="AW300" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX300" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>118923301</v>
+      </c>
+      <c r="B301" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr"/>
+      <c r="J301" t="inlineStr"/>
+      <c r="K301" t="inlineStr"/>
+      <c r="N301" t="inlineStr"/>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q301" t="n">
+        <v>801389</v>
+      </c>
+      <c r="R301" t="n">
+        <v>7496455</v>
+      </c>
+      <c r="S301" t="n">
+        <v>10</v>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W301" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y301" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD301" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE301" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF301" t="inlineStr"/>
+      <c r="AG301" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT301" t="inlineStr"/>
+      <c r="AW301" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX301" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>118923197</v>
+      </c>
+      <c r="B302" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr"/>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr"/>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q302" t="n">
+        <v>801731</v>
+      </c>
+      <c r="R302" t="n">
+        <v>7496362</v>
+      </c>
+      <c r="S302" t="n">
+        <v>10</v>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W302" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y302" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AC302" t="inlineStr">
+        <is>
+          <t>Ringhack på tre stycken tallar</t>
+        </is>
+      </c>
+      <c r="AD302" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE302" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG302" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT302" t="inlineStr"/>
+      <c r="AW302" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX302" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>118923578</v>
+      </c>
+      <c r="B303" t="n">
+        <v>90504</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr"/>
+      <c r="J303" t="inlineStr"/>
+      <c r="K303" t="inlineStr"/>
+      <c r="N303" t="inlineStr"/>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q303" t="n">
+        <v>801345</v>
+      </c>
+      <c r="R303" t="n">
+        <v>7496844</v>
+      </c>
+      <c r="S303" t="n">
+        <v>10</v>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W303" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y303" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD303" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE303" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF303" t="inlineStr"/>
+      <c r="AG303" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT303" t="inlineStr"/>
+      <c r="AW303" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX303" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>118923260</v>
+      </c>
+      <c r="B304" t="n">
+        <v>90504</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr"/>
+      <c r="J304" t="inlineStr"/>
+      <c r="K304" t="inlineStr"/>
+      <c r="N304" t="inlineStr"/>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q304" t="n">
+        <v>801776</v>
+      </c>
+      <c r="R304" t="n">
+        <v>7496263</v>
+      </c>
+      <c r="S304" t="n">
+        <v>10</v>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V304" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W304" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y304" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD304" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE304" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF304" t="inlineStr"/>
+      <c r="AG304" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT304" t="inlineStr"/>
+      <c r="AW304" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX304" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>118923544</v>
+      </c>
+      <c r="B305" t="n">
+        <v>78566</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>864</v>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr"/>
+      <c r="J305" t="inlineStr"/>
+      <c r="K305" t="inlineStr"/>
+      <c r="N305" t="inlineStr"/>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q305" t="n">
+        <v>801375</v>
+      </c>
+      <c r="R305" t="n">
+        <v>7496657</v>
+      </c>
+      <c r="S305" t="n">
+        <v>10</v>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W305" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y305" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD305" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE305" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF305" t="inlineStr"/>
+      <c r="AG305" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT305" t="inlineStr"/>
+      <c r="AW305" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX305" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>118923139</v>
+      </c>
+      <c r="B306" t="n">
+        <v>90856</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Grantickeporing</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Skeletocutis chrysella</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr"/>
+      <c r="J306" t="inlineStr"/>
+      <c r="K306" t="inlineStr"/>
+      <c r="N306" t="inlineStr"/>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q306" t="n">
+        <v>801589</v>
+      </c>
+      <c r="R306" t="n">
+        <v>7496530</v>
+      </c>
+      <c r="S306" t="n">
+        <v>10</v>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W306" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y306" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD306" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE306" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF306" t="inlineStr"/>
+      <c r="AG306" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT306" t="inlineStr"/>
+      <c r="AW306" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX306" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY306" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -28781,10 +28781,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>118922549</v>
+        <v>118922436</v>
       </c>
       <c r="B256" t="n">
-        <v>90522</v>
+        <v>90906</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -28793,25 +28793,25 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5432</v>
+        <v>4217</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -28824,10 +28824,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>801498</v>
+        <v>801392</v>
       </c>
       <c r="R256" t="n">
-        <v>7496951</v>
+        <v>7497197</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -28887,10 +28887,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>118922573</v>
+        <v>118923301</v>
       </c>
       <c r="B257" t="n">
-        <v>79594</v>
+        <v>78491</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -28899,25 +28899,25 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -28930,10 +28930,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>801542</v>
+        <v>801389</v>
       </c>
       <c r="R257" t="n">
-        <v>7496947</v>
+        <v>7496455</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -28993,10 +28993,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>118923038</v>
+        <v>118923466</v>
       </c>
       <c r="B258" t="n">
-        <v>91294</v>
+        <v>57290</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -29009,26 +29009,39 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>2014</v>
+        <v>100109</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr"/>
-      <c r="J258" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
@@ -29036,10 +29049,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>801511</v>
+        <v>801362</v>
       </c>
       <c r="R258" t="n">
-        <v>7496775</v>
+        <v>7496605</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29080,7 +29093,6 @@
       <c r="AE258" t="b">
         <v>0</v>
       </c>
-      <c r="AF258" t="inlineStr"/>
       <c r="AG258" t="b">
         <v>0</v>
       </c>
@@ -29099,10 +29111,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>118923085</v>
+        <v>118922549</v>
       </c>
       <c r="B259" t="n">
-        <v>78484</v>
+        <v>90529</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -29115,21 +29127,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -29142,10 +29154,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>801450</v>
+        <v>801498</v>
       </c>
       <c r="R259" t="n">
-        <v>7496709</v>
+        <v>7496951</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -29315,10 +29327,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>118922409</v>
+        <v>118923132</v>
       </c>
       <c r="B261" t="n">
-        <v>90858</v>
+        <v>90511</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -29327,25 +29339,25 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -29358,10 +29370,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>801382</v>
+        <v>801589</v>
       </c>
       <c r="R261" t="n">
-        <v>7497242</v>
+        <v>7496530</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29421,10 +29433,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>118923452</v>
+        <v>118923219</v>
       </c>
       <c r="B262" t="n">
-        <v>90522</v>
+        <v>90529</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -29464,10 +29476,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>801301</v>
+        <v>801782</v>
       </c>
       <c r="R262" t="n">
-        <v>7496577</v>
+        <v>7496335</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29527,10 +29539,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>118922594</v>
+        <v>118923242</v>
       </c>
       <c r="B263" t="n">
-        <v>90504</v>
+        <v>57290</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -29543,26 +29555,31 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
-      <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
@@ -29570,10 +29587,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>801537</v>
+        <v>801832</v>
       </c>
       <c r="R263" t="n">
-        <v>7496912</v>
+        <v>7496176</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -29608,13 +29625,17 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>Ringhack på mycket grov gran</t>
+        </is>
+      </c>
       <c r="AD263" t="b">
         <v>0</v>
       </c>
       <c r="AE263" t="b">
         <v>0</v>
       </c>
-      <c r="AF263" t="inlineStr"/>
       <c r="AG263" t="b">
         <v>0</v>
       </c>
@@ -29633,10 +29654,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>118923242</v>
+        <v>118922608</v>
       </c>
       <c r="B264" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -29649,31 +29670,26 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
+      <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
@@ -29681,10 +29697,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>801832</v>
+        <v>801537</v>
       </c>
       <c r="R264" t="n">
-        <v>7496176</v>
+        <v>7496912</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -29719,17 +29735,13 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>Ringhack på mycket grov gran</t>
-        </is>
-      </c>
       <c r="AD264" t="b">
         <v>0</v>
       </c>
       <c r="AE264" t="b">
         <v>0</v>
       </c>
+      <c r="AF264" t="inlineStr"/>
       <c r="AG264" t="b">
         <v>0</v>
       </c>
@@ -29748,10 +29760,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>118923181</v>
+        <v>118922489</v>
       </c>
       <c r="B265" t="n">
-        <v>90899</v>
+        <v>90795</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -29760,25 +29772,25 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>4217</v>
+        <v>658</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -29791,10 +29803,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>801607</v>
+        <v>801375</v>
       </c>
       <c r="R265" t="n">
-        <v>7496461</v>
+        <v>7497165</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -29854,10 +29866,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>118923587</v>
+        <v>118923544</v>
       </c>
       <c r="B266" t="n">
-        <v>57290</v>
+        <v>78573</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -29870,31 +29882,26 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
@@ -29902,10 +29909,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>801360</v>
+        <v>801375</v>
       </c>
       <c r="R266" t="n">
-        <v>7496906</v>
+        <v>7496657</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -29940,17 +29947,13 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC266" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD266" t="b">
         <v>0</v>
       </c>
       <c r="AE266" t="b">
         <v>0</v>
       </c>
+      <c r="AF266" t="inlineStr"/>
       <c r="AG266" t="b">
         <v>0</v>
       </c>
@@ -29969,10 +29972,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>118922492</v>
+        <v>118922573</v>
       </c>
       <c r="B267" t="n">
-        <v>90504</v>
+        <v>79601</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -29981,25 +29984,25 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -30012,10 +30015,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>801375</v>
+        <v>801542</v>
       </c>
       <c r="R267" t="n">
-        <v>7497165</v>
+        <v>7496947</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -30075,10 +30078,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>118922575</v>
+        <v>118923136</v>
       </c>
       <c r="B268" t="n">
-        <v>79600</v>
+        <v>90529</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -30087,25 +30090,25 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -30118,10 +30121,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>801542</v>
+        <v>801589</v>
       </c>
       <c r="R268" t="n">
-        <v>7496947</v>
+        <v>7496530</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -30181,10 +30184,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>118923092</v>
+        <v>118923085</v>
       </c>
       <c r="B269" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -30197,31 +30200,26 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
+      <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr"/>
-      <c r="L269" t="inlineStr"/>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
@@ -30267,17 +30265,13 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD269" t="b">
         <v>0</v>
       </c>
       <c r="AE269" t="b">
         <v>0</v>
       </c>
+      <c r="AF269" t="inlineStr"/>
       <c r="AG269" t="b">
         <v>0</v>
       </c>
@@ -30296,10 +30290,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>118923596</v>
+        <v>118923567</v>
       </c>
       <c r="B270" t="n">
-        <v>90504</v>
+        <v>90529</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -30312,21 +30306,21 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -30339,10 +30333,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>801299</v>
+        <v>801380</v>
       </c>
       <c r="R270" t="n">
-        <v>7496931</v>
+        <v>7496726</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -30402,10 +30396,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>118923124</v>
+        <v>118923305</v>
       </c>
       <c r="B271" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -30445,10 +30439,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>801606</v>
+        <v>801340</v>
       </c>
       <c r="R271" t="n">
-        <v>7496529</v>
+        <v>7496538</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -30508,10 +30502,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>118923466</v>
+        <v>118923184</v>
       </c>
       <c r="B272" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -30524,39 +30518,26 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
       <c r="N272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
@@ -30564,10 +30545,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>801362</v>
+        <v>801607</v>
       </c>
       <c r="R272" t="n">
-        <v>7496605</v>
+        <v>7496461</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -30608,6 +30589,7 @@
       <c r="AE272" t="b">
         <v>0</v>
       </c>
+      <c r="AF272" t="inlineStr"/>
       <c r="AG272" t="b">
         <v>0</v>
       </c>
@@ -30626,10 +30608,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>118923225</v>
+        <v>118923587</v>
       </c>
       <c r="B273" t="n">
-        <v>90522</v>
+        <v>57290</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -30642,26 +30624,31 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
@@ -30669,10 +30656,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>801833</v>
+        <v>801360</v>
       </c>
       <c r="R273" t="n">
-        <v>7496271</v>
+        <v>7496906</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -30707,13 +30694,17 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD273" t="b">
         <v>0</v>
       </c>
       <c r="AE273" t="b">
         <v>0</v>
       </c>
-      <c r="AF273" t="inlineStr"/>
       <c r="AG273" t="b">
         <v>0</v>
       </c>
@@ -30735,7 +30726,7 @@
         <v>118923214</v>
       </c>
       <c r="B274" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -30838,10 +30829,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>118923059</v>
+        <v>118923225</v>
       </c>
       <c r="B275" t="n">
-        <v>57134</v>
+        <v>90529</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -30850,39 +30841,30 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>100096</v>
+        <v>5432</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
@@ -30890,10 +30872,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>801503</v>
+        <v>801833</v>
       </c>
       <c r="R275" t="n">
-        <v>7496772</v>
+        <v>7496271</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -30934,6 +30916,7 @@
       <c r="AE275" t="b">
         <v>0</v>
       </c>
+      <c r="AF275" t="inlineStr"/>
       <c r="AG275" t="b">
         <v>0</v>
       </c>
@@ -30952,10 +30935,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>118923112</v>
+        <v>118923258</v>
       </c>
       <c r="B276" t="n">
-        <v>90522</v>
+        <v>90795</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -30968,21 +30951,21 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -30995,10 +30978,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>801607</v>
+        <v>801776</v>
       </c>
       <c r="R276" t="n">
-        <v>7496562</v>
+        <v>7496263</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -31058,10 +31041,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>118922552</v>
+        <v>118923181</v>
       </c>
       <c r="B277" t="n">
-        <v>78484</v>
+        <v>90906</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -31070,25 +31053,25 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -31101,10 +31084,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>801498</v>
+        <v>801607</v>
       </c>
       <c r="R277" t="n">
-        <v>7496951</v>
+        <v>7496461</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -31164,10 +31147,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>118923136</v>
+        <v>118923038</v>
       </c>
       <c r="B278" t="n">
-        <v>90522</v>
+        <v>91301</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -31180,21 +31163,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>5432</v>
+        <v>2014</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -31207,10 +31190,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>801589</v>
+        <v>801511</v>
       </c>
       <c r="R278" t="n">
-        <v>7496530</v>
+        <v>7496775</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -31270,10 +31253,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>118922592</v>
+        <v>118923100</v>
       </c>
       <c r="B279" t="n">
-        <v>90500</v>
+        <v>90529</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -31286,21 +31269,21 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -31313,10 +31296,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>801537</v>
+        <v>801455</v>
       </c>
       <c r="R279" t="n">
-        <v>7496912</v>
+        <v>7496698</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -31376,10 +31359,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>118923055</v>
+        <v>118922409</v>
       </c>
       <c r="B280" t="n">
-        <v>56635</v>
+        <v>90865</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -31388,39 +31371,30 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100065</v>
+        <v>1506</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
         <is>
@@ -31428,10 +31402,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>801503</v>
+        <v>801382</v>
       </c>
       <c r="R280" t="n">
-        <v>7496772</v>
+        <v>7497242</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -31472,6 +31446,7 @@
       <c r="AE280" t="b">
         <v>0</v>
       </c>
+      <c r="AF280" t="inlineStr"/>
       <c r="AG280" t="b">
         <v>0</v>
       </c>
@@ -31490,10 +31465,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>118923184</v>
+        <v>118923092</v>
       </c>
       <c r="B281" t="n">
-        <v>90522</v>
+        <v>57290</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -31506,26 +31481,31 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
@@ -31533,10 +31513,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>801607</v>
+        <v>801450</v>
       </c>
       <c r="R281" t="n">
-        <v>7496461</v>
+        <v>7496709</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -31571,13 +31551,17 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD281" t="b">
         <v>0</v>
       </c>
       <c r="AE281" t="b">
         <v>0</v>
       </c>
-      <c r="AF281" t="inlineStr"/>
       <c r="AG281" t="b">
         <v>0</v>
       </c>
@@ -31596,10 +31580,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>118923557</v>
+        <v>118923139</v>
       </c>
       <c r="B282" t="n">
-        <v>57290</v>
+        <v>90856</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -31608,35 +31592,30 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
+      <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr"/>
-      <c r="L282" t="inlineStr"/>
-      <c r="M282" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
@@ -31644,10 +31623,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>801368</v>
+        <v>801589</v>
       </c>
       <c r="R282" t="n">
-        <v>7496734</v>
+        <v>7496530</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -31682,17 +31661,13 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC282" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD282" t="b">
         <v>0</v>
       </c>
       <c r="AE282" t="b">
         <v>0</v>
       </c>
+      <c r="AF282" t="inlineStr"/>
       <c r="AG282" t="b">
         <v>0</v>
       </c>
@@ -31711,10 +31686,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>118922436</v>
+        <v>118923452</v>
       </c>
       <c r="B283" t="n">
-        <v>90899</v>
+        <v>90529</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -31723,25 +31698,25 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>4217</v>
+        <v>5432</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
@@ -31754,10 +31729,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>801392</v>
+        <v>801301</v>
       </c>
       <c r="R283" t="n">
-        <v>7497197</v>
+        <v>7496577</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -31820,7 +31795,7 @@
         <v>118922600</v>
       </c>
       <c r="B284" t="n">
-        <v>90847</v>
+        <v>90854</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -31923,10 +31898,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>118923219</v>
+        <v>118923616</v>
       </c>
       <c r="B285" t="n">
-        <v>90522</v>
+        <v>78491</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -31939,21 +31914,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -31966,10 +31941,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>801782</v>
+        <v>801355</v>
       </c>
       <c r="R285" t="n">
-        <v>7496335</v>
+        <v>7497040</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -32029,10 +32004,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>118922608</v>
+        <v>118923075</v>
       </c>
       <c r="B286" t="n">
-        <v>78484</v>
+        <v>90529</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -32045,21 +32020,21 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
@@ -32072,10 +32047,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>801537</v>
+        <v>801454</v>
       </c>
       <c r="R286" t="n">
-        <v>7496912</v>
+        <v>7496759</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -32135,10 +32110,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>118922478</v>
+        <v>118923112</v>
       </c>
       <c r="B287" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -32151,31 +32126,26 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
+      <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr"/>
-      <c r="L287" t="inlineStr"/>
-      <c r="M287" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N287" t="inlineStr"/>
       <c r="P287" t="inlineStr">
         <is>
@@ -32183,10 +32153,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>801386</v>
+        <v>801607</v>
       </c>
       <c r="R287" t="n">
-        <v>7497188</v>
+        <v>7496562</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -32221,17 +32191,13 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC287" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD287" t="b">
         <v>0</v>
       </c>
       <c r="AE287" t="b">
         <v>0</v>
       </c>
+      <c r="AF287" t="inlineStr"/>
       <c r="AG287" t="b">
         <v>0</v>
       </c>
@@ -32250,10 +32216,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>118923305</v>
+        <v>118922594</v>
       </c>
       <c r="B288" t="n">
-        <v>78484</v>
+        <v>90511</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -32266,21 +32232,21 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
@@ -32293,10 +32259,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>801340</v>
+        <v>801537</v>
       </c>
       <c r="R288" t="n">
-        <v>7496538</v>
+        <v>7496912</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -32356,10 +32322,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>118923050</v>
+        <v>118923197</v>
       </c>
       <c r="B289" t="n">
-        <v>90522</v>
+        <v>57290</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -32372,26 +32338,31 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
-      <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr"/>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N289" t="inlineStr"/>
       <c r="P289" t="inlineStr">
         <is>
@@ -32399,10 +32370,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>801503</v>
+        <v>801731</v>
       </c>
       <c r="R289" t="n">
-        <v>7496772</v>
+        <v>7496362</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -32437,13 +32408,17 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC289" t="inlineStr">
+        <is>
+          <t>Ringhack på tre stycken tallar</t>
+        </is>
+      </c>
       <c r="AD289" t="b">
         <v>0</v>
       </c>
       <c r="AE289" t="b">
         <v>0</v>
       </c>
-      <c r="AF289" t="inlineStr"/>
       <c r="AG289" t="b">
         <v>0</v>
       </c>
@@ -32462,10 +32437,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>118923258</v>
+        <v>118922492</v>
       </c>
       <c r="B290" t="n">
-        <v>90788</v>
+        <v>90511</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -32478,21 +32453,21 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
@@ -32505,10 +32480,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>801776</v>
+        <v>801375</v>
       </c>
       <c r="R290" t="n">
-        <v>7496263</v>
+        <v>7497165</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -32568,10 +32543,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>118923567</v>
+        <v>118922592</v>
       </c>
       <c r="B291" t="n">
-        <v>90522</v>
+        <v>90507</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -32584,21 +32559,21 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
@@ -32611,10 +32586,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>801380</v>
+        <v>801537</v>
       </c>
       <c r="R291" t="n">
-        <v>7496726</v>
+        <v>7496912</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -32674,10 +32649,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>118923132</v>
+        <v>118922478</v>
       </c>
       <c r="B292" t="n">
-        <v>90504</v>
+        <v>57290</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -32690,26 +32665,31 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
-      <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr"/>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N292" t="inlineStr"/>
       <c r="P292" t="inlineStr">
         <is>
@@ -32717,10 +32697,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>801589</v>
+        <v>801386</v>
       </c>
       <c r="R292" t="n">
-        <v>7496530</v>
+        <v>7497188</v>
       </c>
       <c r="S292" t="n">
         <v>10</v>
@@ -32755,13 +32735,17 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC292" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD292" t="b">
         <v>0</v>
       </c>
       <c r="AE292" t="b">
         <v>0</v>
       </c>
-      <c r="AF292" t="inlineStr"/>
       <c r="AG292" t="b">
         <v>0</v>
       </c>
@@ -32780,10 +32764,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>118923100</v>
+        <v>118922505</v>
       </c>
       <c r="B293" t="n">
-        <v>90522</v>
+        <v>57290</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -32796,26 +32780,31 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
-      <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N293" t="inlineStr"/>
       <c r="P293" t="inlineStr">
         <is>
@@ -32823,10 +32812,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>801455</v>
+        <v>801406</v>
       </c>
       <c r="R293" t="n">
-        <v>7496698</v>
+        <v>7497090</v>
       </c>
       <c r="S293" t="n">
         <v>10</v>
@@ -32861,13 +32850,17 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC293" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD293" t="b">
         <v>0</v>
       </c>
       <c r="AE293" t="b">
         <v>0</v>
       </c>
-      <c r="AF293" t="inlineStr"/>
       <c r="AG293" t="b">
         <v>0</v>
       </c>
@@ -32886,10 +32879,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>118923075</v>
+        <v>118922552</v>
       </c>
       <c r="B294" t="n">
-        <v>90522</v>
+        <v>78491</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -32902,21 +32895,21 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
@@ -32929,10 +32922,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>801454</v>
+        <v>801498</v>
       </c>
       <c r="R294" t="n">
-        <v>7496759</v>
+        <v>7496951</v>
       </c>
       <c r="S294" t="n">
         <v>10</v>
@@ -32992,7 +32985,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>118922505</v>
+        <v>118923531</v>
       </c>
       <c r="B295" t="n">
         <v>57290</v>
@@ -33040,10 +33033,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>801406</v>
+        <v>801373</v>
       </c>
       <c r="R295" t="n">
-        <v>7497090</v>
+        <v>7496663</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -33076,11 +33069,6 @@
       <c r="AA295" t="inlineStr">
         <is>
           <t>2024-08-03</t>
-        </is>
-      </c>
-      <c r="AC295" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -33107,10 +33095,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>118922489</v>
+        <v>118923557</v>
       </c>
       <c r="B296" t="n">
-        <v>90788</v>
+        <v>57290</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -33123,26 +33111,31 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
-      <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N296" t="inlineStr"/>
       <c r="P296" t="inlineStr">
         <is>
@@ -33150,10 +33143,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>801375</v>
+        <v>801368</v>
       </c>
       <c r="R296" t="n">
-        <v>7497165</v>
+        <v>7496734</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -33188,13 +33181,17 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC296" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD296" t="b">
         <v>0</v>
       </c>
       <c r="AE296" t="b">
         <v>0</v>
       </c>
-      <c r="AF296" t="inlineStr"/>
       <c r="AG296" t="b">
         <v>0</v>
       </c>
@@ -33213,10 +33210,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>118923531</v>
+        <v>118923055</v>
       </c>
       <c r="B297" t="n">
-        <v>57290</v>
+        <v>56635</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -33225,20 +33222,20 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>100109</v>
+        <v>100065</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -33246,12 +33243,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I297" t="inlineStr"/>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K297" t="inlineStr"/>
       <c r="L297" t="inlineStr"/>
       <c r="M297" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N297" t="inlineStr"/>
@@ -33261,10 +33262,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>801373</v>
+        <v>801503</v>
       </c>
       <c r="R297" t="n">
-        <v>7496663</v>
+        <v>7496772</v>
       </c>
       <c r="S297" t="n">
         <v>10</v>
@@ -33323,10 +33324,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>118923616</v>
+        <v>118923578</v>
       </c>
       <c r="B298" t="n">
-        <v>78484</v>
+        <v>90511</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -33339,21 +33340,21 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
@@ -33366,10 +33367,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>801355</v>
+        <v>801345</v>
       </c>
       <c r="R298" t="n">
-        <v>7497040</v>
+        <v>7496844</v>
       </c>
       <c r="S298" t="n">
         <v>10</v>
@@ -33429,10 +33430,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>118922367</v>
+        <v>118923596</v>
       </c>
       <c r="B299" t="n">
-        <v>57290</v>
+        <v>90511</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -33445,31 +33446,26 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
+      <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr"/>
-      <c r="L299" t="inlineStr"/>
-      <c r="M299" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N299" t="inlineStr"/>
       <c r="P299" t="inlineStr">
         <is>
@@ -33477,10 +33473,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>801313</v>
+        <v>801299</v>
       </c>
       <c r="R299" t="n">
-        <v>7497257</v>
+        <v>7496931</v>
       </c>
       <c r="S299" t="n">
         <v>10</v>
@@ -33515,17 +33511,13 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC299" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD299" t="b">
         <v>0</v>
       </c>
       <c r="AE299" t="b">
         <v>0</v>
       </c>
+      <c r="AF299" t="inlineStr"/>
       <c r="AG299" t="b">
         <v>0</v>
       </c>
@@ -33544,10 +33536,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>118922460</v>
+        <v>118923124</v>
       </c>
       <c r="B300" t="n">
-        <v>90522</v>
+        <v>78491</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -33560,21 +33552,21 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
@@ -33587,10 +33579,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>801386</v>
+        <v>801606</v>
       </c>
       <c r="R300" t="n">
-        <v>7497188</v>
+        <v>7496529</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -33650,10 +33642,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>118923301</v>
+        <v>118922367</v>
       </c>
       <c r="B301" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -33666,26 +33658,31 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
-      <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N301" t="inlineStr"/>
       <c r="P301" t="inlineStr">
         <is>
@@ -33693,10 +33690,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>801389</v>
+        <v>801313</v>
       </c>
       <c r="R301" t="n">
-        <v>7496455</v>
+        <v>7497257</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -33731,13 +33728,17 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC301" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD301" t="b">
         <v>0</v>
       </c>
       <c r="AE301" t="b">
         <v>0</v>
       </c>
-      <c r="AF301" t="inlineStr"/>
       <c r="AG301" t="b">
         <v>0</v>
       </c>
@@ -33756,10 +33757,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>118923197</v>
+        <v>118922460</v>
       </c>
       <c r="B302" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -33772,31 +33773,26 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
+      <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr"/>
-      <c r="L302" t="inlineStr"/>
-      <c r="M302" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N302" t="inlineStr"/>
       <c r="P302" t="inlineStr">
         <is>
@@ -33804,10 +33800,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>801731</v>
+        <v>801386</v>
       </c>
       <c r="R302" t="n">
-        <v>7496362</v>
+        <v>7497188</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -33842,17 +33838,13 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC302" t="inlineStr">
-        <is>
-          <t>Ringhack på tre stycken tallar</t>
-        </is>
-      </c>
       <c r="AD302" t="b">
         <v>0</v>
       </c>
       <c r="AE302" t="b">
         <v>0</v>
       </c>
+      <c r="AF302" t="inlineStr"/>
       <c r="AG302" t="b">
         <v>0</v>
       </c>
@@ -33871,10 +33863,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>118923578</v>
+        <v>118922575</v>
       </c>
       <c r="B303" t="n">
-        <v>90504</v>
+        <v>79607</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -33883,25 +33875,25 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
@@ -33914,10 +33906,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>801345</v>
+        <v>801542</v>
       </c>
       <c r="R303" t="n">
-        <v>7496844</v>
+        <v>7496947</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -33980,7 +33972,7 @@
         <v>118923260</v>
       </c>
       <c r="B304" t="n">
-        <v>90504</v>
+        <v>90511</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -34083,10 +34075,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>118923544</v>
+        <v>118923059</v>
       </c>
       <c r="B305" t="n">
-        <v>78566</v>
+        <v>57134</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -34095,30 +34087,39 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>864</v>
+        <v>100096</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I305" t="inlineStr"/>
-      <c r="J305" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N305" t="inlineStr"/>
       <c r="P305" t="inlineStr">
         <is>
@@ -34126,10 +34127,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>801375</v>
+        <v>801503</v>
       </c>
       <c r="R305" t="n">
-        <v>7496657</v>
+        <v>7496772</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -34170,7 +34171,6 @@
       <c r="AE305" t="b">
         <v>0</v>
       </c>
-      <c r="AF305" t="inlineStr"/>
       <c r="AG305" t="b">
         <v>0</v>
       </c>
@@ -34189,10 +34189,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>118923139</v>
+        <v>118923050</v>
       </c>
       <c r="B306" t="n">
-        <v>90856</v>
+        <v>90529</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -34201,25 +34201,25 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>2063</v>
+        <v>5432</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
@@ -34232,10 +34232,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>801589</v>
+        <v>801503</v>
       </c>
       <c r="R306" t="n">
-        <v>7496530</v>
+        <v>7496772</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -31792,10 +31792,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>118922600</v>
+        <v>118923616</v>
       </c>
       <c r="B284" t="n">
-        <v>90854</v>
+        <v>78491</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -31804,25 +31804,25 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -31835,10 +31835,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>801537</v>
+        <v>801355</v>
       </c>
       <c r="R284" t="n">
-        <v>7496912</v>
+        <v>7497040</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -31898,10 +31898,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>118923616</v>
+        <v>118923075</v>
       </c>
       <c r="B285" t="n">
-        <v>78491</v>
+        <v>90529</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -31914,21 +31914,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -31941,10 +31941,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>801355</v>
+        <v>801454</v>
       </c>
       <c r="R285" t="n">
-        <v>7497040</v>
+        <v>7496759</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -32004,7 +32004,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>118923075</v>
+        <v>118923112</v>
       </c>
       <c r="B286" t="n">
         <v>90529</v>
@@ -32047,10 +32047,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>801454</v>
+        <v>801607</v>
       </c>
       <c r="R286" t="n">
-        <v>7496759</v>
+        <v>7496562</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -32110,10 +32110,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>118923112</v>
+        <v>118922594</v>
       </c>
       <c r="B287" t="n">
-        <v>90529</v>
+        <v>90511</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -32126,21 +32126,21 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
@@ -32153,10 +32153,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>801607</v>
+        <v>801537</v>
       </c>
       <c r="R287" t="n">
-        <v>7496562</v>
+        <v>7496912</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -32216,10 +32216,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>118922594</v>
+        <v>118923197</v>
       </c>
       <c r="B288" t="n">
-        <v>90511</v>
+        <v>57290</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -32232,26 +32232,31 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
-      <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N288" t="inlineStr"/>
       <c r="P288" t="inlineStr">
         <is>
@@ -32259,10 +32264,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>801537</v>
+        <v>801731</v>
       </c>
       <c r="R288" t="n">
-        <v>7496912</v>
+        <v>7496362</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -32297,13 +32302,17 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>Ringhack på tre stycken tallar</t>
+        </is>
+      </c>
       <c r="AD288" t="b">
         <v>0</v>
       </c>
       <c r="AE288" t="b">
         <v>0</v>
       </c>
-      <c r="AF288" t="inlineStr"/>
       <c r="AG288" t="b">
         <v>0</v>
       </c>
@@ -32322,10 +32331,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>118923197</v>
+        <v>118922492</v>
       </c>
       <c r="B289" t="n">
-        <v>57290</v>
+        <v>90511</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -32338,31 +32347,26 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
+      <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr"/>
-      <c r="L289" t="inlineStr"/>
-      <c r="M289" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N289" t="inlineStr"/>
       <c r="P289" t="inlineStr">
         <is>
@@ -32370,10 +32374,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>801731</v>
+        <v>801375</v>
       </c>
       <c r="R289" t="n">
-        <v>7496362</v>
+        <v>7497165</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -32408,17 +32412,13 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC289" t="inlineStr">
-        <is>
-          <t>Ringhack på tre stycken tallar</t>
-        </is>
-      </c>
       <c r="AD289" t="b">
         <v>0</v>
       </c>
       <c r="AE289" t="b">
         <v>0</v>
       </c>
+      <c r="AF289" t="inlineStr"/>
       <c r="AG289" t="b">
         <v>0</v>
       </c>
@@ -32437,10 +32437,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>118922492</v>
+        <v>118922592</v>
       </c>
       <c r="B290" t="n">
-        <v>90511</v>
+        <v>90507</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -32453,21 +32453,21 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
@@ -32480,10 +32480,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>801375</v>
+        <v>801537</v>
       </c>
       <c r="R290" t="n">
-        <v>7497165</v>
+        <v>7496912</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -32543,10 +32543,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>118922592</v>
+        <v>118922478</v>
       </c>
       <c r="B291" t="n">
-        <v>90507</v>
+        <v>57290</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -32559,26 +32559,31 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
-      <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr"/>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N291" t="inlineStr"/>
       <c r="P291" t="inlineStr">
         <is>
@@ -32586,10 +32591,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>801537</v>
+        <v>801386</v>
       </c>
       <c r="R291" t="n">
-        <v>7496912</v>
+        <v>7497188</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -32624,13 +32629,17 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC291" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD291" t="b">
         <v>0</v>
       </c>
       <c r="AE291" t="b">
         <v>0</v>
       </c>
-      <c r="AF291" t="inlineStr"/>
       <c r="AG291" t="b">
         <v>0</v>
       </c>
@@ -32649,7 +32658,7 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>118922478</v>
+        <v>118922505</v>
       </c>
       <c r="B292" t="n">
         <v>57290</v>
@@ -32697,10 +32706,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>801386</v>
+        <v>801406</v>
       </c>
       <c r="R292" t="n">
-        <v>7497188</v>
+        <v>7497090</v>
       </c>
       <c r="S292" t="n">
         <v>10</v>
@@ -32764,10 +32773,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>118922505</v>
+        <v>118922552</v>
       </c>
       <c r="B293" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -32780,31 +32789,26 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
+      <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr"/>
-      <c r="L293" t="inlineStr"/>
-      <c r="M293" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N293" t="inlineStr"/>
       <c r="P293" t="inlineStr">
         <is>
@@ -32812,10 +32816,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>801406</v>
+        <v>801498</v>
       </c>
       <c r="R293" t="n">
-        <v>7497090</v>
+        <v>7496951</v>
       </c>
       <c r="S293" t="n">
         <v>10</v>
@@ -32850,17 +32854,13 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC293" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD293" t="b">
         <v>0</v>
       </c>
       <c r="AE293" t="b">
         <v>0</v>
       </c>
+      <c r="AF293" t="inlineStr"/>
       <c r="AG293" t="b">
         <v>0</v>
       </c>
@@ -32879,10 +32879,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>118922552</v>
+        <v>118923531</v>
       </c>
       <c r="B294" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -32895,26 +32895,31 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
-      <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N294" t="inlineStr"/>
       <c r="P294" t="inlineStr">
         <is>
@@ -32922,10 +32927,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>801498</v>
+        <v>801373</v>
       </c>
       <c r="R294" t="n">
-        <v>7496951</v>
+        <v>7496663</v>
       </c>
       <c r="S294" t="n">
         <v>10</v>
@@ -32966,7 +32971,6 @@
       <c r="AE294" t="b">
         <v>0</v>
       </c>
-      <c r="AF294" t="inlineStr"/>
       <c r="AG294" t="b">
         <v>0</v>
       </c>
@@ -32985,7 +32989,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>118923531</v>
+        <v>118923557</v>
       </c>
       <c r="B295" t="n">
         <v>57290</v>
@@ -33033,10 +33037,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>801373</v>
+        <v>801368</v>
       </c>
       <c r="R295" t="n">
-        <v>7496663</v>
+        <v>7496734</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -33069,6 +33073,11 @@
       <c r="AA295" t="inlineStr">
         <is>
           <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AC295" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -33095,10 +33104,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>118923557</v>
+        <v>118923055</v>
       </c>
       <c r="B296" t="n">
-        <v>57290</v>
+        <v>56635</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -33107,20 +33116,20 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>100109</v>
+        <v>100065</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -33128,12 +33137,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I296" t="inlineStr"/>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr"/>
       <c r="M296" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N296" t="inlineStr"/>
@@ -33143,10 +33156,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>801368</v>
+        <v>801503</v>
       </c>
       <c r="R296" t="n">
-        <v>7496734</v>
+        <v>7496772</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -33179,11 +33192,6 @@
       <c r="AA296" t="inlineStr">
         <is>
           <t>2024-08-03</t>
-        </is>
-      </c>
-      <c r="AC296" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD296" t="b">
@@ -33210,10 +33218,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>118923055</v>
+        <v>118923578</v>
       </c>
       <c r="B297" t="n">
-        <v>56635</v>
+        <v>90511</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -33222,39 +33230,30 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>100065</v>
+        <v>1202</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr"/>
+      <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr"/>
-      <c r="L297" t="inlineStr"/>
-      <c r="M297" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N297" t="inlineStr"/>
       <c r="P297" t="inlineStr">
         <is>
@@ -33262,10 +33261,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>801503</v>
+        <v>801345</v>
       </c>
       <c r="R297" t="n">
-        <v>7496772</v>
+        <v>7496844</v>
       </c>
       <c r="S297" t="n">
         <v>10</v>
@@ -33306,6 +33305,7 @@
       <c r="AE297" t="b">
         <v>0</v>
       </c>
+      <c r="AF297" t="inlineStr"/>
       <c r="AG297" t="b">
         <v>0</v>
       </c>
@@ -33324,7 +33324,7 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>118923578</v>
+        <v>118923596</v>
       </c>
       <c r="B298" t="n">
         <v>90511</v>
@@ -33367,10 +33367,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>801345</v>
+        <v>801299</v>
       </c>
       <c r="R298" t="n">
-        <v>7496844</v>
+        <v>7496931</v>
       </c>
       <c r="S298" t="n">
         <v>10</v>
@@ -33430,10 +33430,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>118923596</v>
+        <v>118923124</v>
       </c>
       <c r="B299" t="n">
-        <v>90511</v>
+        <v>78491</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -33446,21 +33446,21 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
@@ -33473,10 +33473,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>801299</v>
+        <v>801606</v>
       </c>
       <c r="R299" t="n">
-        <v>7496931</v>
+        <v>7496529</v>
       </c>
       <c r="S299" t="n">
         <v>10</v>
@@ -33536,10 +33536,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>118923124</v>
+        <v>118922367</v>
       </c>
       <c r="B300" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -33552,26 +33552,31 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
-      <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr"/>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N300" t="inlineStr"/>
       <c r="P300" t="inlineStr">
         <is>
@@ -33579,10 +33584,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>801606</v>
+        <v>801313</v>
       </c>
       <c r="R300" t="n">
-        <v>7496529</v>
+        <v>7497257</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -33617,13 +33622,17 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC300" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD300" t="b">
         <v>0</v>
       </c>
       <c r="AE300" t="b">
         <v>0</v>
       </c>
-      <c r="AF300" t="inlineStr"/>
       <c r="AG300" t="b">
         <v>0</v>
       </c>
@@ -33642,10 +33651,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>118922367</v>
+        <v>118922460</v>
       </c>
       <c r="B301" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -33658,31 +33667,26 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
+      <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr"/>
-      <c r="L301" t="inlineStr"/>
-      <c r="M301" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N301" t="inlineStr"/>
       <c r="P301" t="inlineStr">
         <is>
@@ -33690,10 +33694,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>801313</v>
+        <v>801386</v>
       </c>
       <c r="R301" t="n">
-        <v>7497257</v>
+        <v>7497188</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -33728,17 +33732,13 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC301" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD301" t="b">
         <v>0</v>
       </c>
       <c r="AE301" t="b">
         <v>0</v>
       </c>
+      <c r="AF301" t="inlineStr"/>
       <c r="AG301" t="b">
         <v>0</v>
       </c>
@@ -33757,10 +33757,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>118922460</v>
+        <v>118922575</v>
       </c>
       <c r="B302" t="n">
-        <v>90529</v>
+        <v>79607</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -33769,25 +33769,25 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -33800,10 +33800,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>801386</v>
+        <v>801542</v>
       </c>
       <c r="R302" t="n">
-        <v>7497188</v>
+        <v>7496947</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -33863,10 +33863,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>118922575</v>
+        <v>118923260</v>
       </c>
       <c r="B303" t="n">
-        <v>79607</v>
+        <v>90511</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -33875,25 +33875,25 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
@@ -33906,10 +33906,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>801542</v>
+        <v>801776</v>
       </c>
       <c r="R303" t="n">
-        <v>7496947</v>
+        <v>7496263</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -33969,10 +33969,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>118923260</v>
+        <v>118923059</v>
       </c>
       <c r="B304" t="n">
-        <v>90511</v>
+        <v>57134</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -33981,30 +33981,39 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>1202</v>
+        <v>100096</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I304" t="inlineStr"/>
-      <c r="J304" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N304" t="inlineStr"/>
       <c r="P304" t="inlineStr">
         <is>
@@ -34012,10 +34021,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>801776</v>
+        <v>801503</v>
       </c>
       <c r="R304" t="n">
-        <v>7496263</v>
+        <v>7496772</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -34056,7 +34065,6 @@
       <c r="AE304" t="b">
         <v>0</v>
       </c>
-      <c r="AF304" t="inlineStr"/>
       <c r="AG304" t="b">
         <v>0</v>
       </c>
@@ -34075,10 +34083,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>118923059</v>
+        <v>118923050</v>
       </c>
       <c r="B305" t="n">
-        <v>57134</v>
+        <v>90529</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -34087,39 +34095,30 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>100096</v>
+        <v>5432</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I305" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr"/>
+      <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr"/>
-      <c r="L305" t="inlineStr"/>
-      <c r="M305" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N305" t="inlineStr"/>
       <c r="P305" t="inlineStr">
         <is>
@@ -34171,6 +34170,7 @@
       <c r="AE305" t="b">
         <v>0</v>
       </c>
+      <c r="AF305" t="inlineStr"/>
       <c r="AG305" t="b">
         <v>0</v>
       </c>
@@ -34189,10 +34189,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>118923050</v>
+        <v>118922600</v>
       </c>
       <c r="B306" t="n">
-        <v>90529</v>
+        <v>90854</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -34201,25 +34201,25 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>5432</v>
+        <v>2062</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
@@ -34232,10 +34232,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>801503</v>
+        <v>801537</v>
       </c>
       <c r="R306" t="n">
-        <v>7496772</v>
+        <v>7496912</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -28781,10 +28781,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>118922436</v>
+        <v>118923258</v>
       </c>
       <c r="B256" t="n">
-        <v>90906</v>
+        <v>90795</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -28793,25 +28793,25 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>4217</v>
+        <v>658</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -28824,10 +28824,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>801392</v>
+        <v>801776</v>
       </c>
       <c r="R256" t="n">
-        <v>7497197</v>
+        <v>7496263</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -28887,10 +28887,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>118923301</v>
+        <v>118923139</v>
       </c>
       <c r="B257" t="n">
-        <v>78491</v>
+        <v>90856</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -28899,25 +28899,25 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6425</v>
+        <v>2063</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -28930,10 +28930,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>801389</v>
+        <v>801589</v>
       </c>
       <c r="R257" t="n">
-        <v>7496455</v>
+        <v>7496530</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -28993,10 +28993,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>118923466</v>
+        <v>118923059</v>
       </c>
       <c r="B258" t="n">
-        <v>57290</v>
+        <v>57134</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -29005,20 +29005,20 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>100109</v>
+        <v>100096</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -29028,18 +29028,14 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L258" t="inlineStr"/>
       <c r="M258" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N258" t="inlineStr"/>
@@ -29049,10 +29045,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>801362</v>
+        <v>801503</v>
       </c>
       <c r="R258" t="n">
-        <v>7496605</v>
+        <v>7496772</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29111,7 +29107,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>118922549</v>
+        <v>118923567</v>
       </c>
       <c r="B259" t="n">
         <v>90529</v>
@@ -29154,10 +29150,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>801498</v>
+        <v>801380</v>
       </c>
       <c r="R259" t="n">
-        <v>7496951</v>
+        <v>7496726</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -29217,7 +29213,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>118923437</v>
+        <v>118923092</v>
       </c>
       <c r="B260" t="n">
         <v>57290</v>
@@ -29255,7 +29251,7 @@
       <c r="L260" t="inlineStr"/>
       <c r="M260" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N260" t="inlineStr"/>
@@ -29265,10 +29261,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>801301</v>
+        <v>801450</v>
       </c>
       <c r="R260" t="n">
-        <v>7496577</v>
+        <v>7496709</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -29301,6 +29297,11 @@
       <c r="AA260" t="inlineStr">
         <is>
           <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -29327,10 +29328,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>118923132</v>
+        <v>118922367</v>
       </c>
       <c r="B261" t="n">
-        <v>90511</v>
+        <v>57290</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -29343,26 +29344,31 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
-      <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
@@ -29370,10 +29376,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>801589</v>
+        <v>801313</v>
       </c>
       <c r="R261" t="n">
-        <v>7496530</v>
+        <v>7497257</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29408,13 +29414,17 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD261" t="b">
         <v>0</v>
       </c>
       <c r="AE261" t="b">
         <v>0</v>
       </c>
-      <c r="AF261" t="inlineStr"/>
       <c r="AG261" t="b">
         <v>0</v>
       </c>
@@ -29433,7 +29443,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>118923219</v>
+        <v>118923100</v>
       </c>
       <c r="B262" t="n">
         <v>90529</v>
@@ -29476,10 +29486,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>801782</v>
+        <v>801455</v>
       </c>
       <c r="R262" t="n">
-        <v>7496335</v>
+        <v>7496698</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29539,10 +29549,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>118923242</v>
+        <v>118922573</v>
       </c>
       <c r="B263" t="n">
-        <v>57290</v>
+        <v>79601</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -29551,35 +29561,30 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
+      <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
@@ -29587,10 +29592,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>801832</v>
+        <v>801542</v>
       </c>
       <c r="R263" t="n">
-        <v>7496176</v>
+        <v>7496947</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -29625,17 +29630,13 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC263" t="inlineStr">
-        <is>
-          <t>Ringhack på mycket grov gran</t>
-        </is>
-      </c>
       <c r="AD263" t="b">
         <v>0</v>
       </c>
       <c r="AE263" t="b">
         <v>0</v>
       </c>
+      <c r="AF263" t="inlineStr"/>
       <c r="AG263" t="b">
         <v>0</v>
       </c>
@@ -29654,10 +29655,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>118922608</v>
+        <v>118923242</v>
       </c>
       <c r="B264" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -29670,26 +29671,31 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
-      <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
@@ -29697,10 +29703,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>801537</v>
+        <v>801832</v>
       </c>
       <c r="R264" t="n">
-        <v>7496912</v>
+        <v>7496176</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -29735,13 +29741,17 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>Ringhack på mycket grov gran</t>
+        </is>
+      </c>
       <c r="AD264" t="b">
         <v>0</v>
       </c>
       <c r="AE264" t="b">
         <v>0</v>
       </c>
-      <c r="AF264" t="inlineStr"/>
       <c r="AG264" t="b">
         <v>0</v>
       </c>
@@ -29760,10 +29770,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>118922489</v>
+        <v>118923197</v>
       </c>
       <c r="B265" t="n">
-        <v>90795</v>
+        <v>57290</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -29776,26 +29786,31 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
-      <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
@@ -29803,10 +29818,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>801375</v>
+        <v>801731</v>
       </c>
       <c r="R265" t="n">
-        <v>7497165</v>
+        <v>7496362</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -29841,13 +29856,17 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>Ringhack på tre stycken tallar</t>
+        </is>
+      </c>
       <c r="AD265" t="b">
         <v>0</v>
       </c>
       <c r="AE265" t="b">
         <v>0</v>
       </c>
-      <c r="AF265" t="inlineStr"/>
       <c r="AG265" t="b">
         <v>0</v>
       </c>
@@ -29866,10 +29885,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>118923544</v>
+        <v>118923219</v>
       </c>
       <c r="B266" t="n">
-        <v>78573</v>
+        <v>90529</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -29882,21 +29901,21 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -29909,10 +29928,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>801375</v>
+        <v>801782</v>
       </c>
       <c r="R266" t="n">
-        <v>7496657</v>
+        <v>7496335</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -29972,10 +29991,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>118922573</v>
+        <v>118923124</v>
       </c>
       <c r="B267" t="n">
-        <v>79601</v>
+        <v>78491</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -29984,25 +30003,25 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -30015,10 +30034,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>801542</v>
+        <v>801606</v>
       </c>
       <c r="R267" t="n">
-        <v>7496947</v>
+        <v>7496529</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -30078,10 +30097,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>118923136</v>
+        <v>118923085</v>
       </c>
       <c r="B268" t="n">
-        <v>90529</v>
+        <v>78491</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -30094,21 +30113,21 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -30121,10 +30140,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>801589</v>
+        <v>801450</v>
       </c>
       <c r="R268" t="n">
-        <v>7496530</v>
+        <v>7496709</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -30184,10 +30203,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>118923085</v>
+        <v>118922594</v>
       </c>
       <c r="B269" t="n">
-        <v>78491</v>
+        <v>90511</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -30200,21 +30219,21 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -30227,10 +30246,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>801450</v>
+        <v>801537</v>
       </c>
       <c r="R269" t="n">
-        <v>7496709</v>
+        <v>7496912</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -30290,10 +30309,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>118923567</v>
+        <v>118923038</v>
       </c>
       <c r="B270" t="n">
-        <v>90529</v>
+        <v>91301</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -30306,21 +30325,21 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>5432</v>
+        <v>2014</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -30333,10 +30352,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>801380</v>
+        <v>801511</v>
       </c>
       <c r="R270" t="n">
-        <v>7496726</v>
+        <v>7496775</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -30396,10 +30415,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>118923305</v>
+        <v>118923531</v>
       </c>
       <c r="B271" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -30412,26 +30431,31 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
-      <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
@@ -30439,10 +30463,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>801340</v>
+        <v>801373</v>
       </c>
       <c r="R271" t="n">
-        <v>7496538</v>
+        <v>7496663</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -30483,7 +30507,6 @@
       <c r="AE271" t="b">
         <v>0</v>
       </c>
-      <c r="AF271" t="inlineStr"/>
       <c r="AG271" t="b">
         <v>0</v>
       </c>
@@ -30502,10 +30525,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>118923184</v>
+        <v>118923214</v>
       </c>
       <c r="B272" t="n">
-        <v>90529</v>
+        <v>78491</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -30518,21 +30541,21 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -30545,10 +30568,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>801607</v>
+        <v>801782</v>
       </c>
       <c r="R272" t="n">
-        <v>7496461</v>
+        <v>7496335</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -30608,10 +30631,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>118923587</v>
+        <v>118922552</v>
       </c>
       <c r="B273" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -30624,31 +30647,26 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
@@ -30656,10 +30674,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>801360</v>
+        <v>801498</v>
       </c>
       <c r="R273" t="n">
-        <v>7496906</v>
+        <v>7496951</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -30694,17 +30712,13 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD273" t="b">
         <v>0</v>
       </c>
       <c r="AE273" t="b">
         <v>0</v>
       </c>
+      <c r="AF273" t="inlineStr"/>
       <c r="AG273" t="b">
         <v>0</v>
       </c>
@@ -30723,10 +30737,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>118923214</v>
+        <v>118923136</v>
       </c>
       <c r="B274" t="n">
-        <v>78491</v>
+        <v>90529</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -30739,21 +30753,21 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -30766,10 +30780,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>801782</v>
+        <v>801589</v>
       </c>
       <c r="R274" t="n">
-        <v>7496335</v>
+        <v>7496530</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -30829,7 +30843,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>118923225</v>
+        <v>118923452</v>
       </c>
       <c r="B275" t="n">
         <v>90529</v>
@@ -30872,10 +30886,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>801833</v>
+        <v>801301</v>
       </c>
       <c r="R275" t="n">
-        <v>7496271</v>
+        <v>7496577</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -30935,10 +30949,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>118923258</v>
+        <v>118922436</v>
       </c>
       <c r="B276" t="n">
-        <v>90795</v>
+        <v>90906</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -30947,25 +30961,25 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>658</v>
+        <v>4217</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -30978,10 +30992,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>801776</v>
+        <v>801392</v>
       </c>
       <c r="R276" t="n">
-        <v>7496263</v>
+        <v>7497197</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -31041,10 +31055,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>118923181</v>
+        <v>118922592</v>
       </c>
       <c r="B277" t="n">
-        <v>90906</v>
+        <v>90507</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -31053,25 +31067,25 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>4217</v>
+        <v>1108</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -31084,10 +31098,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>801607</v>
+        <v>801537</v>
       </c>
       <c r="R277" t="n">
-        <v>7496461</v>
+        <v>7496912</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -31147,10 +31161,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>118923038</v>
+        <v>118922409</v>
       </c>
       <c r="B278" t="n">
-        <v>91301</v>
+        <v>90865</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -31159,25 +31173,25 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>2014</v>
+        <v>1506</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -31190,10 +31204,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>801511</v>
+        <v>801382</v>
       </c>
       <c r="R278" t="n">
-        <v>7496775</v>
+        <v>7497242</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -31253,7 +31267,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>118923100</v>
+        <v>118923112</v>
       </c>
       <c r="B279" t="n">
         <v>90529</v>
@@ -31296,10 +31310,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>801455</v>
+        <v>801607</v>
       </c>
       <c r="R279" t="n">
-        <v>7496698</v>
+        <v>7496562</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -31359,10 +31373,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>118922409</v>
+        <v>118922505</v>
       </c>
       <c r="B280" t="n">
-        <v>90865</v>
+        <v>57290</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -31371,30 +31385,35 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
         <is>
@@ -31402,10 +31421,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>801382</v>
+        <v>801406</v>
       </c>
       <c r="R280" t="n">
-        <v>7497242</v>
+        <v>7497090</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -31440,13 +31459,17 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC280" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD280" t="b">
         <v>0</v>
       </c>
       <c r="AE280" t="b">
         <v>0</v>
       </c>
-      <c r="AF280" t="inlineStr"/>
       <c r="AG280" t="b">
         <v>0</v>
       </c>
@@ -31465,7 +31488,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>118923092</v>
+        <v>118922478</v>
       </c>
       <c r="B281" t="n">
         <v>57290</v>
@@ -31513,10 +31536,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>801450</v>
+        <v>801386</v>
       </c>
       <c r="R281" t="n">
-        <v>7496709</v>
+        <v>7497188</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -31580,10 +31603,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>118923139</v>
+        <v>118923301</v>
       </c>
       <c r="B282" t="n">
-        <v>90856</v>
+        <v>78491</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -31592,25 +31615,25 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>2063</v>
+        <v>6425</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -31623,10 +31646,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>801589</v>
+        <v>801389</v>
       </c>
       <c r="R282" t="n">
-        <v>7496530</v>
+        <v>7496455</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -31686,10 +31709,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>118923452</v>
+        <v>118923132</v>
       </c>
       <c r="B283" t="n">
-        <v>90529</v>
+        <v>90511</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -31702,21 +31725,21 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
@@ -31729,10 +31752,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>801301</v>
+        <v>801589</v>
       </c>
       <c r="R283" t="n">
-        <v>7496577</v>
+        <v>7496530</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -31792,10 +31815,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>118923616</v>
+        <v>118922489</v>
       </c>
       <c r="B284" t="n">
-        <v>78491</v>
+        <v>90795</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -31808,21 +31831,21 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -31835,10 +31858,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>801355</v>
+        <v>801375</v>
       </c>
       <c r="R284" t="n">
-        <v>7497040</v>
+        <v>7497165</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -31898,10 +31921,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>118923075</v>
+        <v>118923578</v>
       </c>
       <c r="B285" t="n">
-        <v>90529</v>
+        <v>90511</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -31914,21 +31937,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -31941,10 +31964,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>801454</v>
+        <v>801345</v>
       </c>
       <c r="R285" t="n">
-        <v>7496759</v>
+        <v>7496844</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -32004,10 +32027,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>118923112</v>
+        <v>118923587</v>
       </c>
       <c r="B286" t="n">
-        <v>90529</v>
+        <v>57290</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -32020,26 +32043,31 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
-      <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N286" t="inlineStr"/>
       <c r="P286" t="inlineStr">
         <is>
@@ -32047,10 +32075,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>801607</v>
+        <v>801360</v>
       </c>
       <c r="R286" t="n">
-        <v>7496562</v>
+        <v>7496906</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -32085,13 +32113,17 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC286" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD286" t="b">
         <v>0</v>
       </c>
       <c r="AE286" t="b">
         <v>0</v>
       </c>
-      <c r="AF286" t="inlineStr"/>
       <c r="AG286" t="b">
         <v>0</v>
       </c>
@@ -32110,10 +32142,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>118922594</v>
+        <v>118923544</v>
       </c>
       <c r="B287" t="n">
-        <v>90511</v>
+        <v>78573</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -32126,21 +32158,21 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
@@ -32153,10 +32185,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>801537</v>
+        <v>801375</v>
       </c>
       <c r="R287" t="n">
-        <v>7496912</v>
+        <v>7496657</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -32216,7 +32248,7 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>118923197</v>
+        <v>118923557</v>
       </c>
       <c r="B288" t="n">
         <v>57290</v>
@@ -32264,10 +32296,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>801731</v>
+        <v>801368</v>
       </c>
       <c r="R288" t="n">
-        <v>7496362</v>
+        <v>7496734</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -32304,7 +32336,7 @@
       </c>
       <c r="AC288" t="inlineStr">
         <is>
-          <t>Ringhack på tre stycken tallar</t>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -32331,10 +32363,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>118922492</v>
+        <v>118922460</v>
       </c>
       <c r="B289" t="n">
-        <v>90511</v>
+        <v>90529</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -32347,21 +32379,21 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
@@ -32374,10 +32406,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>801375</v>
+        <v>801386</v>
       </c>
       <c r="R289" t="n">
-        <v>7497165</v>
+        <v>7497188</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -32437,10 +32469,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>118922592</v>
+        <v>118923055</v>
       </c>
       <c r="B290" t="n">
-        <v>90507</v>
+        <v>56635</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -32449,30 +32481,39 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>1108</v>
+        <v>100065</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I290" t="inlineStr"/>
-      <c r="J290" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr"/>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N290" t="inlineStr"/>
       <c r="P290" t="inlineStr">
         <is>
@@ -32480,10 +32521,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>801537</v>
+        <v>801503</v>
       </c>
       <c r="R290" t="n">
-        <v>7496912</v>
+        <v>7496772</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -32524,7 +32565,6 @@
       <c r="AE290" t="b">
         <v>0</v>
       </c>
-      <c r="AF290" t="inlineStr"/>
       <c r="AG290" t="b">
         <v>0</v>
       </c>
@@ -32543,10 +32583,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>118922478</v>
+        <v>118922608</v>
       </c>
       <c r="B291" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -32559,31 +32599,26 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
+      <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr"/>
-      <c r="L291" t="inlineStr"/>
-      <c r="M291" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N291" t="inlineStr"/>
       <c r="P291" t="inlineStr">
         <is>
@@ -32591,10 +32626,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>801386</v>
+        <v>801537</v>
       </c>
       <c r="R291" t="n">
-        <v>7497188</v>
+        <v>7496912</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -32629,17 +32664,13 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC291" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD291" t="b">
         <v>0</v>
       </c>
       <c r="AE291" t="b">
         <v>0</v>
       </c>
+      <c r="AF291" t="inlineStr"/>
       <c r="AG291" t="b">
         <v>0</v>
       </c>
@@ -32658,10 +32689,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>118922505</v>
+        <v>118923181</v>
       </c>
       <c r="B292" t="n">
-        <v>57290</v>
+        <v>90906</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -32670,35 +32701,30 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
+      <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr"/>
-      <c r="L292" t="inlineStr"/>
-      <c r="M292" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N292" t="inlineStr"/>
       <c r="P292" t="inlineStr">
         <is>
@@ -32706,10 +32732,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>801406</v>
+        <v>801607</v>
       </c>
       <c r="R292" t="n">
-        <v>7497090</v>
+        <v>7496461</v>
       </c>
       <c r="S292" t="n">
         <v>10</v>
@@ -32744,17 +32770,13 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC292" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD292" t="b">
         <v>0</v>
       </c>
       <c r="AE292" t="b">
         <v>0</v>
       </c>
+      <c r="AF292" t="inlineStr"/>
       <c r="AG292" t="b">
         <v>0</v>
       </c>
@@ -32773,10 +32795,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>118922552</v>
+        <v>118923596</v>
       </c>
       <c r="B293" t="n">
-        <v>78491</v>
+        <v>90511</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -32789,21 +32811,21 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
@@ -32816,10 +32838,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>801498</v>
+        <v>801299</v>
       </c>
       <c r="R293" t="n">
-        <v>7496951</v>
+        <v>7496931</v>
       </c>
       <c r="S293" t="n">
         <v>10</v>
@@ -32879,10 +32901,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>118923531</v>
+        <v>118923050</v>
       </c>
       <c r="B294" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -32895,31 +32917,26 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
+      <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr"/>
-      <c r="L294" t="inlineStr"/>
-      <c r="M294" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N294" t="inlineStr"/>
       <c r="P294" t="inlineStr">
         <is>
@@ -32927,10 +32944,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>801373</v>
+        <v>801503</v>
       </c>
       <c r="R294" t="n">
-        <v>7496663</v>
+        <v>7496772</v>
       </c>
       <c r="S294" t="n">
         <v>10</v>
@@ -32971,6 +32988,7 @@
       <c r="AE294" t="b">
         <v>0</v>
       </c>
+      <c r="AF294" t="inlineStr"/>
       <c r="AG294" t="b">
         <v>0</v>
       </c>
@@ -32989,10 +33007,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>118923557</v>
+        <v>118923225</v>
       </c>
       <c r="B295" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -33005,31 +33023,26 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
+      <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr"/>
-      <c r="L295" t="inlineStr"/>
-      <c r="M295" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N295" t="inlineStr"/>
       <c r="P295" t="inlineStr">
         <is>
@@ -33037,10 +33050,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>801368</v>
+        <v>801833</v>
       </c>
       <c r="R295" t="n">
-        <v>7496734</v>
+        <v>7496271</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -33075,17 +33088,13 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC295" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD295" t="b">
         <v>0</v>
       </c>
       <c r="AE295" t="b">
         <v>0</v>
       </c>
+      <c r="AF295" t="inlineStr"/>
       <c r="AG295" t="b">
         <v>0</v>
       </c>
@@ -33104,10 +33113,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>118923055</v>
+        <v>118923184</v>
       </c>
       <c r="B296" t="n">
-        <v>56635</v>
+        <v>90529</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -33116,39 +33125,30 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>100065</v>
+        <v>5432</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I296" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr"/>
+      <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
-      <c r="M296" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N296" t="inlineStr"/>
       <c r="P296" t="inlineStr">
         <is>
@@ -33156,10 +33156,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>801503</v>
+        <v>801607</v>
       </c>
       <c r="R296" t="n">
-        <v>7496772</v>
+        <v>7496461</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -33200,6 +33200,7 @@
       <c r="AE296" t="b">
         <v>0</v>
       </c>
+      <c r="AF296" t="inlineStr"/>
       <c r="AG296" t="b">
         <v>0</v>
       </c>
@@ -33218,10 +33219,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>118923578</v>
+        <v>118923426</v>
       </c>
       <c r="B297" t="n">
-        <v>90511</v>
+        <v>57290</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -33234,26 +33235,31 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
-      <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N297" t="inlineStr"/>
       <c r="P297" t="inlineStr">
         <is>
@@ -33261,10 +33267,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>801345</v>
+        <v>801301</v>
       </c>
       <c r="R297" t="n">
-        <v>7496844</v>
+        <v>7496577</v>
       </c>
       <c r="S297" t="n">
         <v>10</v>
@@ -33299,13 +33305,17 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC297" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD297" t="b">
         <v>0</v>
       </c>
       <c r="AE297" t="b">
         <v>0</v>
       </c>
-      <c r="AF297" t="inlineStr"/>
       <c r="AG297" t="b">
         <v>0</v>
       </c>
@@ -33324,10 +33334,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>118923596</v>
+        <v>118923075</v>
       </c>
       <c r="B298" t="n">
-        <v>90511</v>
+        <v>90529</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -33340,21 +33350,21 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
@@ -33367,10 +33377,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>801299</v>
+        <v>801454</v>
       </c>
       <c r="R298" t="n">
-        <v>7496931</v>
+        <v>7496759</v>
       </c>
       <c r="S298" t="n">
         <v>10</v>
@@ -33430,10 +33440,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>118923124</v>
+        <v>118923466</v>
       </c>
       <c r="B299" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -33446,26 +33456,39 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I299" t="inlineStr"/>
-      <c r="J299" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N299" t="inlineStr"/>
       <c r="P299" t="inlineStr">
         <is>
@@ -33473,10 +33496,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>801606</v>
+        <v>801362</v>
       </c>
       <c r="R299" t="n">
-        <v>7496529</v>
+        <v>7496605</v>
       </c>
       <c r="S299" t="n">
         <v>10</v>
@@ -33517,7 +33540,6 @@
       <c r="AE299" t="b">
         <v>0</v>
       </c>
-      <c r="AF299" t="inlineStr"/>
       <c r="AG299" t="b">
         <v>0</v>
       </c>
@@ -33536,10 +33558,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>118922367</v>
+        <v>118922575</v>
       </c>
       <c r="B300" t="n">
-        <v>57290</v>
+        <v>79607</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -33548,35 +33570,30 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
+      <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr"/>
-      <c r="L300" t="inlineStr"/>
-      <c r="M300" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N300" t="inlineStr"/>
       <c r="P300" t="inlineStr">
         <is>
@@ -33584,10 +33601,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>801313</v>
+        <v>801542</v>
       </c>
       <c r="R300" t="n">
-        <v>7497257</v>
+        <v>7496947</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -33622,17 +33639,13 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC300" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD300" t="b">
         <v>0</v>
       </c>
       <c r="AE300" t="b">
         <v>0</v>
       </c>
+      <c r="AF300" t="inlineStr"/>
       <c r="AG300" t="b">
         <v>0</v>
       </c>
@@ -33651,10 +33664,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>118922460</v>
+        <v>118923616</v>
       </c>
       <c r="B301" t="n">
-        <v>90529</v>
+        <v>78491</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -33667,21 +33680,21 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
@@ -33694,10 +33707,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>801386</v>
+        <v>801355</v>
       </c>
       <c r="R301" t="n">
-        <v>7497188</v>
+        <v>7497040</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -33757,10 +33770,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>118922575</v>
+        <v>118923305</v>
       </c>
       <c r="B302" t="n">
-        <v>79607</v>
+        <v>78491</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -33769,20 +33782,20 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -33800,10 +33813,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>801542</v>
+        <v>801340</v>
       </c>
       <c r="R302" t="n">
-        <v>7496947</v>
+        <v>7496538</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -33863,10 +33876,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>118923260</v>
+        <v>118922549</v>
       </c>
       <c r="B303" t="n">
-        <v>90511</v>
+        <v>90529</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -33879,21 +33892,21 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
@@ -33906,10 +33919,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>801776</v>
+        <v>801498</v>
       </c>
       <c r="R303" t="n">
-        <v>7496263</v>
+        <v>7496951</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -33969,10 +33982,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>118923059</v>
+        <v>118922492</v>
       </c>
       <c r="B304" t="n">
-        <v>57134</v>
+        <v>90511</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -33981,39 +33994,30 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>100096</v>
+        <v>1202</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I304" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr"/>
+      <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr"/>
-      <c r="L304" t="inlineStr"/>
-      <c r="M304" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N304" t="inlineStr"/>
       <c r="P304" t="inlineStr">
         <is>
@@ -34021,10 +34025,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>801503</v>
+        <v>801375</v>
       </c>
       <c r="R304" t="n">
-        <v>7496772</v>
+        <v>7497165</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -34065,6 +34069,7 @@
       <c r="AE304" t="b">
         <v>0</v>
       </c>
+      <c r="AF304" t="inlineStr"/>
       <c r="AG304" t="b">
         <v>0</v>
       </c>
@@ -34083,10 +34088,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>118923050</v>
+        <v>118923260</v>
       </c>
       <c r="B305" t="n">
-        <v>90529</v>
+        <v>90511</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -34099,21 +34104,21 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
@@ -34126,10 +34131,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>801503</v>
+        <v>801776</v>
       </c>
       <c r="R305" t="n">
-        <v>7496772</v>
+        <v>7496263</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY306"/>
+  <dimension ref="A1:AY311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34298,6 +34298,536 @@
       </c>
       <c r="AY306" t="inlineStr"/>
     </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>120259845</v>
+      </c>
+      <c r="B307" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr"/>
+      <c r="J307" t="inlineStr"/>
+      <c r="K307" t="inlineStr"/>
+      <c r="N307" t="inlineStr"/>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q307" t="n">
+        <v>801037</v>
+      </c>
+      <c r="R307" t="n">
+        <v>7496691</v>
+      </c>
+      <c r="S307" t="n">
+        <v>10</v>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W307" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y307" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD307" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE307" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF307" t="inlineStr"/>
+      <c r="AG307" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT307" t="inlineStr"/>
+      <c r="AW307" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX307" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>120259848</v>
+      </c>
+      <c r="B308" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr"/>
+      <c r="J308" t="inlineStr"/>
+      <c r="K308" t="inlineStr"/>
+      <c r="N308" t="inlineStr"/>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q308" t="n">
+        <v>801042</v>
+      </c>
+      <c r="R308" t="n">
+        <v>7496699</v>
+      </c>
+      <c r="S308" t="n">
+        <v>10</v>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W308" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y308" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD308" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE308" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF308" t="inlineStr"/>
+      <c r="AG308" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT308" t="inlineStr"/>
+      <c r="AW308" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX308" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>120259847</v>
+      </c>
+      <c r="B309" t="n">
+        <v>90558</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr"/>
+      <c r="J309" t="inlineStr"/>
+      <c r="K309" t="inlineStr"/>
+      <c r="N309" t="inlineStr"/>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q309" t="n">
+        <v>801042</v>
+      </c>
+      <c r="R309" t="n">
+        <v>7496699</v>
+      </c>
+      <c r="S309" t="n">
+        <v>10</v>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W309" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y309" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD309" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE309" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF309" t="inlineStr"/>
+      <c r="AG309" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT309" t="inlineStr"/>
+      <c r="AW309" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX309" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>120259844</v>
+      </c>
+      <c r="B310" t="n">
+        <v>90846</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>658</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr"/>
+      <c r="J310" t="inlineStr"/>
+      <c r="K310" t="inlineStr"/>
+      <c r="N310" t="inlineStr"/>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q310" t="n">
+        <v>801037</v>
+      </c>
+      <c r="R310" t="n">
+        <v>7496691</v>
+      </c>
+      <c r="S310" t="n">
+        <v>10</v>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W310" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y310" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD310" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE310" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF310" t="inlineStr"/>
+      <c r="AG310" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT310" t="inlineStr"/>
+      <c r="AW310" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX310" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>120259843</v>
+      </c>
+      <c r="B311" t="n">
+        <v>90752</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>48</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Lappticka</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr"/>
+      <c r="J311" t="inlineStr"/>
+      <c r="K311" t="inlineStr"/>
+      <c r="N311" t="inlineStr"/>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q311" t="n">
+        <v>801037</v>
+      </c>
+      <c r="R311" t="n">
+        <v>7496691</v>
+      </c>
+      <c r="S311" t="n">
+        <v>10</v>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W311" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y311" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD311" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE311" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF311" t="inlineStr"/>
+      <c r="AG311" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT311" t="inlineStr"/>
+      <c r="AW311" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX311" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY311" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -34300,10 +34300,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>120259845</v>
+        <v>120259847</v>
       </c>
       <c r="B307" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -34316,21 +34316,21 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -34343,10 +34343,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>801037</v>
+        <v>801042</v>
       </c>
       <c r="R307" t="n">
-        <v>7496691</v>
+        <v>7496699</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -34406,10 +34406,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>120259848</v>
+        <v>120259845</v>
       </c>
       <c r="B308" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -34449,10 +34449,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>801042</v>
+        <v>801037</v>
       </c>
       <c r="R308" t="n">
-        <v>7496699</v>
+        <v>7496691</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -34512,10 +34512,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>120259847</v>
+        <v>120259843</v>
       </c>
       <c r="B309" t="n">
-        <v>90558</v>
+        <v>90770</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -34524,25 +34524,25 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>1108</v>
+        <v>48</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -34555,10 +34555,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>801042</v>
+        <v>801037</v>
       </c>
       <c r="R309" t="n">
-        <v>7496699</v>
+        <v>7496691</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -34621,7 +34621,7 @@
         <v>120259844</v>
       </c>
       <c r="B310" t="n">
-        <v>90846</v>
+        <v>90864</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -34724,10 +34724,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>120259843</v>
+        <v>120259848</v>
       </c>
       <c r="B311" t="n">
-        <v>90752</v>
+        <v>78542</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -34736,25 +34736,25 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>48</v>
+        <v>6425</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
@@ -34767,10 +34767,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>801037</v>
+        <v>801042</v>
       </c>
       <c r="R311" t="n">
-        <v>7496691</v>
+        <v>7496699</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -34300,10 +34300,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>120259847</v>
+        <v>120259848</v>
       </c>
       <c r="B307" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -34316,21 +34316,21 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -34406,10 +34406,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>120259845</v>
+        <v>120259843</v>
       </c>
       <c r="B308" t="n">
-        <v>78542</v>
+        <v>90770</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -34418,25 +34418,25 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6425</v>
+        <v>48</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -34512,10 +34512,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>120259843</v>
+        <v>120259844</v>
       </c>
       <c r="B309" t="n">
-        <v>90770</v>
+        <v>90864</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -34524,25 +34524,25 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -34618,10 +34618,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>120259844</v>
+        <v>120259847</v>
       </c>
       <c r="B310" t="n">
-        <v>90864</v>
+        <v>90576</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -34634,21 +34634,21 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
@@ -34661,10 +34661,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>801037</v>
+        <v>801042</v>
       </c>
       <c r="R310" t="n">
-        <v>7496691</v>
+        <v>7496699</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -34724,7 +34724,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>120259848</v>
+        <v>120259845</v>
       </c>
       <c r="B311" t="n">
         <v>78542</v>
@@ -34767,10 +34767,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>801042</v>
+        <v>801037</v>
       </c>
       <c r="R311" t="n">
-        <v>7496699</v>
+        <v>7496691</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -34300,7 +34300,7 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>120259848</v>
+        <v>120259845</v>
       </c>
       <c r="B307" t="n">
         <v>78542</v>
@@ -34343,10 +34343,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>801042</v>
+        <v>801037</v>
       </c>
       <c r="R307" t="n">
-        <v>7496699</v>
+        <v>7496691</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -34406,10 +34406,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>120259843</v>
+        <v>120259844</v>
       </c>
       <c r="B308" t="n">
-        <v>90770</v>
+        <v>90864</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -34418,25 +34418,25 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -34512,10 +34512,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>120259844</v>
+        <v>120259847</v>
       </c>
       <c r="B309" t="n">
-        <v>90864</v>
+        <v>90576</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -34528,21 +34528,21 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -34555,10 +34555,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>801037</v>
+        <v>801042</v>
       </c>
       <c r="R309" t="n">
-        <v>7496691</v>
+        <v>7496699</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -34618,10 +34618,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>120259847</v>
+        <v>120259843</v>
       </c>
       <c r="B310" t="n">
-        <v>90576</v>
+        <v>90770</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -34630,25 +34630,25 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>1108</v>
+        <v>48</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
@@ -34661,10 +34661,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>801042</v>
+        <v>801037</v>
       </c>
       <c r="R310" t="n">
-        <v>7496699</v>
+        <v>7496691</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -34724,7 +34724,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>120259845</v>
+        <v>120259848</v>
       </c>
       <c r="B311" t="n">
         <v>78542</v>
@@ -34767,10 +34767,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>801037</v>
+        <v>801042</v>
       </c>
       <c r="R311" t="n">
-        <v>7496691</v>
+        <v>7496699</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -34406,10 +34406,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>120259844</v>
+        <v>120259848</v>
       </c>
       <c r="B308" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -34422,21 +34422,21 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -34449,10 +34449,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>801037</v>
+        <v>801042</v>
       </c>
       <c r="R308" t="n">
-        <v>7496691</v>
+        <v>7496699</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -34512,10 +34512,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>120259847</v>
+        <v>120259843</v>
       </c>
       <c r="B309" t="n">
-        <v>90576</v>
+        <v>90770</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -34524,25 +34524,25 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>1108</v>
+        <v>48</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -34555,10 +34555,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>801042</v>
+        <v>801037</v>
       </c>
       <c r="R309" t="n">
-        <v>7496699</v>
+        <v>7496691</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -34618,10 +34618,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>120259843</v>
+        <v>120259847</v>
       </c>
       <c r="B310" t="n">
-        <v>90770</v>
+        <v>90576</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -34630,25 +34630,25 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>48</v>
+        <v>1108</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
@@ -34661,10 +34661,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>801037</v>
+        <v>801042</v>
       </c>
       <c r="R310" t="n">
-        <v>7496691</v>
+        <v>7496699</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -34724,10 +34724,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>120259848</v>
+        <v>120259844</v>
       </c>
       <c r="B311" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -34740,21 +34740,21 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
@@ -34767,10 +34767,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>801042</v>
+        <v>801037</v>
       </c>
       <c r="R311" t="n">
-        <v>7496699</v>
+        <v>7496691</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -34300,10 +34300,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>120259845</v>
+        <v>120259843</v>
       </c>
       <c r="B307" t="n">
-        <v>78542</v>
+        <v>90770</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -34312,25 +34312,25 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>6425</v>
+        <v>48</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -34406,7 +34406,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>120259848</v>
+        <v>120259845</v>
       </c>
       <c r="B308" t="n">
         <v>78542</v>
@@ -34449,10 +34449,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>801042</v>
+        <v>801037</v>
       </c>
       <c r="R308" t="n">
-        <v>7496699</v>
+        <v>7496691</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -34512,10 +34512,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>120259843</v>
+        <v>120259848</v>
       </c>
       <c r="B309" t="n">
-        <v>90770</v>
+        <v>78542</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -34524,25 +34524,25 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>48</v>
+        <v>6425</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -34555,10 +34555,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>801037</v>
+        <v>801042</v>
       </c>
       <c r="R309" t="n">
-        <v>7496691</v>
+        <v>7496699</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -34618,10 +34618,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>120259847</v>
+        <v>120259844</v>
       </c>
       <c r="B310" t="n">
-        <v>90576</v>
+        <v>90864</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -34634,21 +34634,21 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
@@ -34661,10 +34661,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>801042</v>
+        <v>801037</v>
       </c>
       <c r="R310" t="n">
-        <v>7496699</v>
+        <v>7496691</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -34724,10 +34724,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>120259844</v>
+        <v>120259847</v>
       </c>
       <c r="B311" t="n">
-        <v>90864</v>
+        <v>90576</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -34740,21 +34740,21 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
@@ -34767,10 +34767,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>801037</v>
+        <v>801042</v>
       </c>
       <c r="R311" t="n">
-        <v>7496691</v>
+        <v>7496699</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -34300,10 +34300,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>120259843</v>
+        <v>120259845</v>
       </c>
       <c r="B307" t="n">
-        <v>90770</v>
+        <v>78542</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -34312,25 +34312,25 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>48</v>
+        <v>6425</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -34406,10 +34406,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>120259845</v>
+        <v>120259843</v>
       </c>
       <c r="B308" t="n">
-        <v>78542</v>
+        <v>90770</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -34418,25 +34418,25 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6425</v>
+        <v>48</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -34300,10 +34300,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>120259845</v>
+        <v>120259843</v>
       </c>
       <c r="B307" t="n">
-        <v>78542</v>
+        <v>90770</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -34312,25 +34312,25 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>6425</v>
+        <v>48</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -34406,10 +34406,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>120259843</v>
+        <v>120259848</v>
       </c>
       <c r="B308" t="n">
-        <v>90770</v>
+        <v>78542</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -34418,25 +34418,25 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>48</v>
+        <v>6425</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -34449,10 +34449,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>801037</v>
+        <v>801042</v>
       </c>
       <c r="R308" t="n">
-        <v>7496691</v>
+        <v>7496699</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -34512,10 +34512,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>120259848</v>
+        <v>120259847</v>
       </c>
       <c r="B309" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -34528,21 +34528,21 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -34618,10 +34618,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>120259844</v>
+        <v>120259845</v>
       </c>
       <c r="B310" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -34634,21 +34634,21 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
@@ -34724,10 +34724,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>120259847</v>
+        <v>120259844</v>
       </c>
       <c r="B311" t="n">
-        <v>90576</v>
+        <v>90864</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -34740,21 +34740,21 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
@@ -34767,10 +34767,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>801042</v>
+        <v>801037</v>
       </c>
       <c r="R311" t="n">
-        <v>7496699</v>
+        <v>7496691</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -34300,10 +34300,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>120259843</v>
+        <v>120259845</v>
       </c>
       <c r="B307" t="n">
-        <v>90770</v>
+        <v>78542</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -34312,25 +34312,25 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>48</v>
+        <v>6425</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -34406,10 +34406,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>120259848</v>
+        <v>120259847</v>
       </c>
       <c r="B308" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -34422,21 +34422,21 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -34512,10 +34512,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>120259847</v>
+        <v>120259844</v>
       </c>
       <c r="B309" t="n">
-        <v>90576</v>
+        <v>90864</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -34528,21 +34528,21 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -34555,10 +34555,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>801042</v>
+        <v>801037</v>
       </c>
       <c r="R309" t="n">
-        <v>7496699</v>
+        <v>7496691</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -34618,7 +34618,7 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>120259845</v>
+        <v>120259848</v>
       </c>
       <c r="B310" t="n">
         <v>78542</v>
@@ -34661,10 +34661,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>801037</v>
+        <v>801042</v>
       </c>
       <c r="R310" t="n">
-        <v>7496691</v>
+        <v>7496699</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -34724,10 +34724,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>120259844</v>
+        <v>120259843</v>
       </c>
       <c r="B311" t="n">
-        <v>90864</v>
+        <v>90770</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -34736,25 +34736,25 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -15080,11 +15080,11 @@
         <v>115316427</v>
       </c>
       <c r="B130" t="n">
-        <v>56470</v>
+        <v>56585</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -15080,7 +15080,7 @@
         <v>115316427</v>
       </c>
       <c r="B130" t="n">
-        <v>56585</v>
+        <v>56586</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15313,11 +15313,11 @@
         <v>115319264</v>
       </c>
       <c r="B132" t="n">
-        <v>57281</v>
+        <v>57400</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -30391,11 +30391,11 @@
         <v>118923466</v>
       </c>
       <c r="B271" t="n">
-        <v>57292</v>
+        <v>57384</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -13518,11 +13518,11 @@
         <v>114993749</v>
       </c>
       <c r="B116" t="n">
-        <v>56478</v>
+        <v>56687</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -13747,11 +13747,11 @@
         <v>114993651</v>
       </c>
       <c r="B118" t="n">
-        <v>56478</v>
+        <v>56687</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -17512,11 +17512,11 @@
         <v>115319335</v>
       </c>
       <c r="B152" t="n">
-        <v>56478</v>
+        <v>56687</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">

--- a/artfynd/A 61481-2023 artfynd.xlsx
+++ b/artfynd/A 61481-2023 artfynd.xlsx
@@ -13518,7 +13518,7 @@
         <v>114993749</v>
       </c>
       <c r="B116" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>114993651</v>
       </c>
       <c r="B118" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>115319335</v>
       </c>
       <c r="B152" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
